--- a/demo.xlsx
+++ b/demo.xlsx
@@ -60,7 +60,7 @@
     <t>UNET</t>
   </si>
   <si>
-    <t>rd</t>
+    <t>rt</t>
   </si>
   <si>
     <t>loopback</t>
@@ -656,8 +656,8 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="str">
-        <f>198&amp;"."&amp;162&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
-        <v>198.162.0.31</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+        <v>172.16.0.31</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>28</v>
@@ -948,8 +948,8 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="str">
-        <f>198&amp;"."&amp;162&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
-        <v>198.162.0.32</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+        <v>172.16.0.32</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>28</v>
@@ -1219,8 +1219,8 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="str">
-        <f>198&amp;"."&amp;162&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
-        <v>198.162.0.33</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+        <v>172.16.0.33</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>28</v>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="40">
   <si>
     <t>site</t>
   </si>
@@ -21,7 +21,28 @@
     <t>intf_prefix</t>
   </si>
   <si>
-    <t>g0/</t>
+    <t>router-id</t>
+  </si>
+  <si>
+    <t>brukernavn</t>
+  </si>
+  <si>
+    <t>passord</t>
+  </si>
+  <si>
+    <t>vty_lines</t>
+  </si>
+  <si>
+    <t>E0/</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>cisco</t>
+  </si>
+  <si>
+    <t>0 - 4</t>
   </si>
   <si>
     <t>vrf</t>
@@ -94,6 +115,12 @@
   </si>
   <si>
     <t>network-id</t>
+  </si>
+  <si>
+    <t>ipsec</t>
+  </si>
+  <si>
+    <t>ipsec key</t>
   </si>
   <si>
     <t>tunnel 30</t>
@@ -161,13 +188,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -424,275 +453,310 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>1.1.1.0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
         <v>10.0</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>0.0</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="6" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.11.0.0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="6" t="str">
         <f t="shared" ref="E5:E7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="str">
+      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="2">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.11.255.254")</f>
         <v>10.11.255.254</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="A6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="7">
         <v>20.0</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>0.0</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="6" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.21.0.0</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.21.0.1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="str">
+      <c r="F6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10.21.0.1</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.21.255.254")</f>
         <v>10.21.255.254</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="7">
         <v>30.0</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>0.0</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="6" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.31.0.0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.31.0.1</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="4" t="str">
+      <c r="F7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10.31.0.1</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.31.255.254")</f>
         <v>10.31.255.254</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
+      <c r="B10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="6">
         <v>10.0</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>1.1.1.10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6">
         <v>20.0</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>1.1.1.20</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6">
         <v>30.0</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>1.1.1.30</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.31</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="4" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;0</f>
-        <v>1.1.1.0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>30</v>
+      <c r="D15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+        <v>1.1.1.30</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="H15" s="1">
         <v>30.0</v>
       </c>
+      <c r="I15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -716,257 +780,292 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>2.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
         <v>10.0</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>0.0</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="6" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.12.0.0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="6" t="str">
         <f t="shared" ref="E5:E7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="str">
+      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="2">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.12.255.254")</f>
         <v>10.12.255.254</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="A6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="7">
         <v>20.0</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>0.0</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="6" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.22.0.0</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.22.0.1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="str">
+      <c r="F6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10.22.0.1</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.22.255.254")</f>
         <v>10.22.255.254</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="7">
         <v>30.0</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>0.0</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="6" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.32.0.0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="4" t="str">
+      <c r="F7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.32.255.254")</f>
         <v>10.32.255.254</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
+      <c r="B10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="6">
         <v>10.0</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>2.2.2.10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6">
         <v>20.0</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>2.2.2.20</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6">
         <v>30.0</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>2.2.2.30</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.32</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="4" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;0</f>
-        <v>2.2.2.0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>30</v>
+      <c r="D15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+        <v>2.2.2.30</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="H15" s="1">
         <v>30.0</v>
       </c>
+      <c r="I15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -987,257 +1086,290 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>3.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
         <v>10.0</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>0.0</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="6" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.13.0.0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="6" t="str">
         <f t="shared" ref="E5:E7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="str">
+      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="2">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.13.255.254")</f>
         <v>10.13.255.254</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="A6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="7">
         <v>20.0</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>0.0</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="6" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.23.0.0</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.23.0.1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="str">
+      <c r="F6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10.23.0.1</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.23.255.254")</f>
         <v>10.23.255.254</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="7">
         <v>30.0</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>0.0</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="6" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.33.0.0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.33.0.1</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="4" t="str">
+      <c r="F7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10.33.0.1</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.33.255.254")</f>
         <v>10.33.255.254</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
+      <c r="B10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="6">
         <v>10.0</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>3.3.3.10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6">
         <v>20.0</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>3.3.3.20</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6">
         <v>30.0</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>3.3.3.30</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.33</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="4" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;0</f>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>30</v>
+      <c r="D15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+        <v>3.3.3.30</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="H15" s="1">
         <v>30.0</v>
       </c>
+      <c r="I15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -1,19 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CE3C44-4C0D-43F3-9C83-D47E97EC6DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Ark 1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Ark 2" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Ark 3" sheetId="3" r:id="rId7"/>
+    <sheet name="Ark 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ark 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Ark 3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="41">
   <si>
     <t>site</t>
   </si>
@@ -123,53 +167,57 @@
     <t>ipsec key</t>
   </si>
   <si>
+    <t>tunnel 10</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>multipoint</t>
+  </si>
+  <si>
     <t>tunnel 30</t>
-  </si>
-  <si>
-    <t>255.255.255.0</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>multipoint</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -179,71 +227,58 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -433,20 +468,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="3" max="4" width="23.88"/>
+    <col min="3" max="4" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,14 +504,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="str">
+      <c r="C2" s="1" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>1.1.1.0</v>
       </c>
@@ -487,215 +525,215 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="6" t="str">
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.11.0.0</v>
       </c>
-      <c r="E5" s="6" t="str">
-        <f t="shared" ref="E5:E7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="E5" s="4" t="str">
+        <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="6" t="str">
-        <f t="shared" ref="G5:G7" si="2">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="G5" s="4" t="str">
+        <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="H5" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.11.255.254")</f>
+      <c r="H5" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.11.255.254")</f>
         <v>10.11.255.254</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7">
-        <v>20.0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="6" t="str">
+      <c r="B6" s="5">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.21.0.0</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.21.0.1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>10.21.0.1</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10.21.0.1</v>
-      </c>
-      <c r="H6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.21.255.254")</f>
+      <c r="H6" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.21.255.254")</f>
         <v>10.21.255.254</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7">
-        <v>30.0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="6" t="str">
+      <c r="B7" s="5">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.31.0.0</v>
       </c>
-      <c r="E7" s="6" t="str">
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.31.0.1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>10.31.0.1</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10.31.0.1</v>
-      </c>
-      <c r="H7" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.31.255.254")</f>
+      <c r="H7" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.31.255.254")</f>
         <v>10.31.255.254</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="9" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="D10" s="6" t="str">
+      <c r="C10" s="4">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>1.1.1.10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D11" s="6" t="str">
+      <c r="C11" s="4">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>1.1.1.20</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="6">
-        <v>30.0</v>
-      </c>
-      <c r="D12" s="6" t="str">
+      <c r="C12" s="4">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>1.1.1.30</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -708,72 +746,96 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="6" t="str">
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
-        <v>172.16.0.31</v>
-      </c>
-      <c r="D15" s="6" t="s">
+        <v>172.16.0.11</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="6" t="str">
+      <c r="E15" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
-        <v>1.1.1.30</v>
-      </c>
-      <c r="F15" s="6" t="s">
+        <v>1.1.1.10</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H15" s="1">
-        <v>30.0</v>
+        <v>10</v>
       </c>
       <c r="I15" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="4" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
+        <v>172.16.0.31</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
+        <v>1.1.1.30</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="1">
+        <v>30</v>
+      </c>
+      <c r="I16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="14.63"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,14 +855,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="1" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>2.2.2.0</v>
       </c>
@@ -814,215 +876,215 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="6" t="str">
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.12.0.0</v>
       </c>
-      <c r="E5" s="6" t="str">
-        <f t="shared" ref="E5:E7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="E5" s="4" t="str">
+        <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="6" t="str">
-        <f t="shared" ref="G5:G7" si="2">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="G5" s="4" t="str">
+        <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="H5" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.12.255.254")</f>
+      <c r="H5" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.12.255.254")</f>
         <v>10.12.255.254</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7">
-        <v>20.0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="6" t="str">
+      <c r="B6" s="5">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.22.0.0</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.22.0.1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>10.22.0.1</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10.22.0.1</v>
-      </c>
-      <c r="H6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.22.255.254")</f>
+      <c r="H6" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.22.255.254")</f>
         <v>10.22.255.254</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7">
-        <v>30.0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="6" t="str">
+      <c r="B7" s="5">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.32.0.0</v>
       </c>
-      <c r="E7" s="6" t="str">
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.32.0.1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10.32.0.1</v>
-      </c>
-      <c r="H7" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.32.255.254")</f>
+      <c r="H7" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.32.255.254")</f>
         <v>10.32.255.254</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="9" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="D10" s="6" t="str">
+      <c r="C10" s="4">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>2.2.2.10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D11" s="6" t="str">
+      <c r="C11" s="4">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>2.2.2.20</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="6">
-        <v>30.0</v>
-      </c>
-      <c r="D12" s="6" t="str">
+      <c r="C12" s="4">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>2.2.2.30</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -1035,51 +1097,86 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+        <v>172.16.0.12</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+        <v>2.2.2.10</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="b" cm="1">
+        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A15 )*( 'Ark 1'!B:B=B15 ),'Ark 1'!I:I)</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="6" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+      <c r="C16" s="4" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.32</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="6" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+      <c r="E16" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
         <v>2.2.2.30</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="I15" s="1" t="b">
+      <c r="H16" s="1">
+        <v>30</v>
+      </c>
+      <c r="I16" s="1" t="b" cm="1">
+        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A16 )*( 'Ark 1'!B:B=B16 ),'Ark 1'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J16" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1099,14 +1196,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="str">
+      <c r="C2" s="1" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>3.3.3.0</v>
       </c>
@@ -1120,215 +1217,215 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="6" t="str">
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.13.0.0</v>
       </c>
-      <c r="E5" s="6" t="str">
-        <f t="shared" ref="E5:E7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="E5" s="4" t="str">
+        <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="6" t="str">
-        <f t="shared" ref="G5:G7" si="2">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="G5" s="4" t="str">
+        <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="H5" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.13.255.254")</f>
+      <c r="H5" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.13.255.254")</f>
         <v>10.13.255.254</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7">
-        <v>20.0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="6" t="str">
+      <c r="B6" s="5">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.23.0.0</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.23.0.1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>10.23.0.1</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10.23.0.1</v>
-      </c>
-      <c r="H6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.23.255.254")</f>
+      <c r="H6" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.23.255.254")</f>
         <v>10.23.255.254</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7">
-        <v>30.0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="6" t="str">
+      <c r="B7" s="5">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.33.0.0</v>
       </c>
-      <c r="E7" s="6" t="str">
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.33.0.1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>10.33.0.1</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10.33.0.1</v>
-      </c>
-      <c r="H7" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.33.255.254")</f>
+      <c r="H7" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.33.255.254")</f>
         <v>10.33.255.254</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="9" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="D10" s="6" t="str">
+      <c r="C10" s="4">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>3.3.3.10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="D11" s="6" t="str">
+      <c r="C11" s="4">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>3.3.3.20</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="6">
-        <v>30.0</v>
-      </c>
-      <c r="D12" s="6" t="str">
+      <c r="C12" s="4">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>3.3.3.30</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -1341,37 +1438,73 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+        <v>172.16.0.13</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+        <v>3.3.3.10</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="b" cm="1">
+        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A15 )*( 'Ark 1'!B:B=B15 ),'Ark 1'!I:I)</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="6" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+      <c r="C16" s="4" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.33</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="6" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+      <c r="E16" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
         <v>3.3.3.30</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6" t="s">
+      <c r="F16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="I15" s="1" t="b">
+      <c r="H16" s="1">
+        <v>30</v>
+      </c>
+      <c r="I16" s="1" t="b" cm="1">
+        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A16 )*( 'Ark 1'!B:B=B16 ),'Ark 1'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J16" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CE3C44-4C0D-43F3-9C83-D47E97EC6DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C44913-C8FF-4ED8-BDE9-50398E4EB678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ark 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Ark 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Ark 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
+    <sheet name="Site 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Site 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Site 4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="42">
   <si>
     <t>site</t>
   </si>
@@ -180,6 +181,9 @@
   </si>
   <si>
     <t>tunnel 30</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
@@ -668,6 +672,9 @@
       <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1125,7 +1132,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1" t="b" cm="1">
-        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A15 )*( 'Ark 1'!B:B=B15 ),'Ark 1'!I:I)</f>
+        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
       <c r="J15" s="1"/>
@@ -1158,7 +1165,7 @@
         <v>30</v>
       </c>
       <c r="I16" s="1" t="b" cm="1">
-        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A16 )*( 'Ark 1'!B:B=B16 ),'Ark 1'!I:I)</f>
+        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
       <c r="J16" s="1"/>
@@ -1466,7 +1473,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1" t="b" cm="1">
-        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A15 )*( 'Ark 1'!B:B=B15 ),'Ark 1'!I:I)</f>
+        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
       <c r="J15" s="1"/>
@@ -1499,7 +1506,349 @@
         <v>30</v>
       </c>
       <c r="I16" s="1" t="b" cm="1">
-        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Ark 1'!A:A=A16 )*( 'Ark 1'!B:B=B16 ),'Ark 1'!I:I)</f>
+        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43CB965-4707-4F05-B33E-53058C2979EF}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>4.4.4.0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="str">
+        <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.14.0.0</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <v>10.14.0.1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="4" t="str">
+        <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <v>10.14.0.1</v>
+      </c>
+      <c r="H5" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.13.255.254")</f>
+        <v>10.13.255.254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="str">
+        <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.24.0.0</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.24.0.1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>10.24.0.1</v>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.23.255.254")</f>
+        <v>10.23.255.254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="str">
+        <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.34.0.0</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.34.0.1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>10.34.0.1</v>
+      </c>
+      <c r="H7" s="4" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.33.255.254")</f>
+        <v>10.33.255.254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
+        <v>4.4.4.10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="4">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
+        <v>4.4.4.20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="4">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
+        <v>4.4.4.30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+        <v>172.16.0.14</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+        <v>4.4.4.10</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="b" cm="1">
+        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="4" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
+        <v>172.16.0.34</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
+        <v>4.4.4.30</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="1">
+        <v>30</v>
+      </c>
+      <c r="I16" s="1" t="b" cm="1">
+        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
       <c r="J16" s="1"/>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C44913-C8FF-4ED8-BDE9-50398E4EB678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEB0EB9-ED56-463C-A2D0-3C524DBED300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -35,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="41">
   <si>
     <t>site</t>
   </si>
@@ -182,14 +160,11 @@
   <si>
     <t>tunnel 30</t>
   </si>
-  <si>
-    <t>n</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -201,7 +176,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -246,30 +220,1058 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="144">
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="16">
+    <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="140"/>
+      <tableStyleElement type="headerRow" dxfId="143"/>
+      <tableStyleElement type="firstRowStripe" dxfId="142"/>
+      <tableStyleElement type="secondRowStripe" dxfId="141"/>
+    </tableStyle>
+    <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="136"/>
+      <tableStyleElement type="headerRow" dxfId="139"/>
+      <tableStyleElement type="firstRowStripe" dxfId="138"/>
+      <tableStyleElement type="secondRowStripe" dxfId="137"/>
+    </tableStyle>
+    <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="132"/>
+      <tableStyleElement type="headerRow" dxfId="135"/>
+      <tableStyleElement type="firstRowStripe" dxfId="134"/>
+      <tableStyleElement type="secondRowStripe" dxfId="133"/>
+    </tableStyle>
+    <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="128"/>
+      <tableStyleElement type="headerRow" dxfId="131"/>
+      <tableStyleElement type="firstRowStripe" dxfId="130"/>
+      <tableStyleElement type="secondRowStripe" dxfId="129"/>
+    </tableStyle>
+    <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="124"/>
+      <tableStyleElement type="headerRow" dxfId="127"/>
+      <tableStyleElement type="firstRowStripe" dxfId="126"/>
+      <tableStyleElement type="secondRowStripe" dxfId="125"/>
+    </tableStyle>
+    <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="120"/>
+      <tableStyleElement type="headerRow" dxfId="123"/>
+      <tableStyleElement type="firstRowStripe" dxfId="122"/>
+      <tableStyleElement type="secondRowStripe" dxfId="121"/>
+    </tableStyle>
+    <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="116"/>
+      <tableStyleElement type="headerRow" dxfId="119"/>
+      <tableStyleElement type="firstRowStripe" dxfId="118"/>
+      <tableStyleElement type="secondRowStripe" dxfId="117"/>
+    </tableStyle>
+    <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="112"/>
+      <tableStyleElement type="headerRow" dxfId="115"/>
+      <tableStyleElement type="firstRowStripe" dxfId="114"/>
+      <tableStyleElement type="secondRowStripe" dxfId="113"/>
+    </tableStyle>
+    <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="108"/>
+      <tableStyleElement type="headerRow" dxfId="111"/>
+      <tableStyleElement type="firstRowStripe" dxfId="110"/>
+      <tableStyleElement type="secondRowStripe" dxfId="109"/>
+    </tableStyle>
+    <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="104"/>
+      <tableStyleElement type="headerRow" dxfId="107"/>
+      <tableStyleElement type="firstRowStripe" dxfId="106"/>
+      <tableStyleElement type="secondRowStripe" dxfId="105"/>
+    </tableStyle>
+    <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
+      <tableStyleElement type="headerRow" dxfId="103"/>
+      <tableStyleElement type="firstRowStripe" dxfId="102"/>
+      <tableStyleElement type="secondRowStripe" dxfId="101"/>
+    </tableStyle>
+    <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="96"/>
+      <tableStyleElement type="headerRow" dxfId="99"/>
+      <tableStyleElement type="firstRowStripe" dxfId="98"/>
+      <tableStyleElement type="secondRowStripe" dxfId="97"/>
+    </tableStyle>
+    <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="92"/>
+      <tableStyleElement type="headerRow" dxfId="95"/>
+      <tableStyleElement type="firstRowStripe" dxfId="94"/>
+      <tableStyleElement type="secondRowStripe" dxfId="93"/>
+    </tableStyle>
+    <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="88"/>
+      <tableStyleElement type="headerRow" dxfId="91"/>
+      <tableStyleElement type="firstRowStripe" dxfId="90"/>
+      <tableStyleElement type="secondRowStripe" dxfId="89"/>
+    </tableStyle>
+    <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
+      <tableStyleElement type="headerRow" dxfId="87"/>
+      <tableStyleElement type="firstRowStripe" dxfId="86"/>
+      <tableStyleElement type="secondRowStripe" dxfId="85"/>
+    </tableStyle>
+    <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="80"/>
+      <tableStyleElement type="headerRow" dxfId="83"/>
+      <tableStyleElement type="firstRowStripe" dxfId="82"/>
+      <tableStyleElement type="secondRowStripe" dxfId="81"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -279,6 +1281,246 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:F2">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="router-id"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 1 (HUB)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell10" displayName="Tabell10" ref="A4:H7" headerRowDxfId="22" dataDxfId="20" totalsRowDxfId="21">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="vrf" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="vlan" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="interface" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="nett id" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="gateway" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="mask" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="address min" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="address max" dataDxfId="23"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 3-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabell11" displayName="Tabell11" ref="A9:D12" headerRowDxfId="15" dataDxfId="13" totalsRowDxfId="14">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="vrf" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="rt" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="loopback" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="laddr" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 3-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell12" displayName="Tabell12" ref="A14:J16" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="tunnel id" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="vrf" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="ip address" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="mask" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="source" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="destination" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="gre mode" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="network-id" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="ipsec" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="ipsec key" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 3-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Tabell13" displayName="Tabell13" ref="A1:F2" headerRowDxfId="73" dataDxfId="71" totalsRowDxfId="72">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="site" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="intf_prefix" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="router-id" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="brukernavn" dataDxfId="76"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0C00-000005000000}" name="passord" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="vty_lines" dataDxfId="74"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Tabell14" displayName="Tabell14" ref="A4:H7" headerRowDxfId="62" dataDxfId="60" totalsRowDxfId="61">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="vrf" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="vlan" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="interface" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="nett id" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="gateway" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="mask" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="address min" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0D00-000008000000}" name="address max" dataDxfId="63"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Tabell15" displayName="Tabell15" ref="A9:D12" headerRowDxfId="55" dataDxfId="53" totalsRowDxfId="54">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="vrf" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="rt" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="loopback" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0E00-000004000000}" name="laddr" dataDxfId="56"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Tabell16" displayName="Tabell16" ref="A14:J16" headerRowDxfId="42" dataDxfId="40" totalsRowDxfId="41">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="tunnel id" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="vrf" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="ip address" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="mask" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="source" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="destination" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="gre mode" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="network-id" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="ipsec" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0F00-00000A000000}" name="ipsec key" dataDxfId="43"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:H7">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="gateway"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 1 (HUB)-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabell7" displayName="Tabell7" ref="A9:D12">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="rt"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="laddr"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 1 (HUB)-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabell8" displayName="Tabell8" ref="A14:J16">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="tunnel id"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="gre mode"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="network-id"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="ipsec"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="ipsec key"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 1 (HUB)-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell1" displayName="Tabell1" ref="A1:F2">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="intf_prefix"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="router-id"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="brukernavn"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="passord"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="vty_lines"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell2" displayName="Tabell2" ref="A4:H7">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="nett id"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="gateway"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell3" displayName="Tabell3" ref="A9:D12">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="rt"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="laddr"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A14:J16">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell9" displayName="Tabell9" ref="A1:F2" headerRowDxfId="33" dataDxfId="31" totalsRowDxfId="32">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="intf_prefix" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="router-id" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="vty_lines" dataDxfId="34"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 3-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -482,13 +1724,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="23.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="6" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,239 +1753,237 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" s="2" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>1.1.1.0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="6" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.11.0.0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="6" t="str">
         <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.11.255.254")</f>
         <v>10.11.255.254</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="7">
         <v>20</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="6" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.21.0.0</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>10.21.0.1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.21.0.1</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.21.255.254")</f>
         <v>10.21.255.254</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="7">
         <v>30</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="6" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.31.0.0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>10.31.0.1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.31.0.1</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.31.255.254")</f>
         <v>10.31.255.254</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H9" t="s">
-        <v>41</v>
-      </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="6">
         <v>10</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>1.1.1.10</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="6">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>1.1.1.20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="6">
         <v>30</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>1.1.1.30</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="5" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -753,81 +1996,1071 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.11</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4" t="str">
+      <c r="E15" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
         <v>1.1.1.10</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="2">
         <v>10</v>
       </c>
-      <c r="I15" s="1" t="b">
+      <c r="I15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="4" t="str">
+      <c r="C16" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.31</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="4" t="str">
+      <c r="E16" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
         <v>1.1.1.30</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
         <v>30</v>
       </c>
-      <c r="I16" s="1" t="b">
+      <c r="I16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
     </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -836,13 +3069,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="6" width="12.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,236 +3100,237 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" s="2" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>2.2.2.0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="6" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.12.0.0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="6" t="str">
         <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.12.255.254")</f>
         <v>10.12.255.254</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="7">
         <v>20</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="6" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.22.0.0</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>10.22.0.1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.22.0.1</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.22.255.254")</f>
         <v>10.22.255.254</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="7">
         <v>30</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="6" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.32.0.0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.32.255.254")</f>
         <v>10.32.255.254</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="6">
         <v>10</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>2.2.2.10</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="6">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>2.2.2.20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="6">
         <v>30</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>2.2.2.30</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="5" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -1104,74 +3343,1065 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.12</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4" t="str">
+      <c r="E15" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
         <v>2.2.2.10</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="2">
         <v>10</v>
       </c>
-      <c r="I15" s="1" t="b" cm="1">
+      <c r="I15" s="2" t="b">
         <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="4" t="str">
+      <c r="C16" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.32</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="4" t="str">
+      <c r="E16" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
         <v>2.2.2.30</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
         <v>30</v>
       </c>
-      <c r="I16" s="1" t="b" cm="1">
+      <c r="I16" s="2" t="b">
         <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="2"/>
     </row>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1180,680 +4410,2846 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="6" width="12.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" s="12" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>3.3.3.0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="12" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="15" t="s">
         <v>17</v>
       </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="17">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="16">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="16" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.13.0.0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="16" t="str">
         <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="16" t="str">
         <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="16" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.13.255.254")</f>
         <v>10.13.255.254</v>
       </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="17">
         <v>20</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="16">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="16" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.23.0.0</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="16" t="str">
         <f t="shared" si="0"/>
         <v>10.23.0.1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="16" t="str">
         <f t="shared" si="1"/>
         <v>10.23.0.1</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="16" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.23.255.254")</f>
         <v>10.23.255.254</v>
       </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="17">
         <v>30</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="16">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="16" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.33.0.0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="16" t="str">
         <f t="shared" si="0"/>
         <v>10.33.0.1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="16" t="str">
         <f t="shared" si="1"/>
         <v>10.33.0.1</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="16" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.33.255.254")</f>
         <v>10.33.255.254</v>
       </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="15" t="s">
         <v>24</v>
       </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="16">
         <v>10</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="16" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>3.3.3.10</v>
       </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="16">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="16" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>3.3.3.20</v>
       </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="16">
         <v>30</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="16" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>3.3.3.30</v>
       </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="10" t="s">
         <v>35</v>
       </c>
+      <c r="K14" s="11"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="16" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.13</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4" t="str">
+      <c r="E15" s="16" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
         <v>3.3.3.10</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="12">
         <v>10</v>
       </c>
-      <c r="I15" s="1" t="b" cm="1">
+      <c r="I15" s="12" t="b">
         <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="4" t="str">
+      <c r="C16" s="16" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.33</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="4" t="str">
+      <c r="E16" s="16" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
         <v>3.3.3.30</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="12">
         <v>30</v>
       </c>
-      <c r="I16" s="1" t="b" cm="1">
+      <c r="I16" s="12" t="b">
         <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="11"/>
     </row>
+    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43CB965-4707-4F05-B33E-53058C2979EF}">
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="1" max="3" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" customWidth="1"/>
+    <col min="11" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="21">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" s="21" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>4.4.4.0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
     </row>
-    <row r="3" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
     </row>
-    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
     </row>
-    <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="6" t="str">
         <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.14.0.0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="6" t="str">
         <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.14.0.1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.14.0.1</v>
       </c>
-      <c r="H5" s="4" t="str">
-        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.13.255.254")</f>
-        <v>10.13.255.254</v>
-      </c>
+      <c r="H5" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.14.255.254")</f>
+        <v>10.14.255.254</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
     </row>
-    <row r="6" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="7">
         <v>20</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="6" t="str">
         <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.24.0.0</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>10.24.0.1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.24.0.1</v>
       </c>
-      <c r="H6" s="4" t="str">
-        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.23.255.254")</f>
-        <v>10.23.255.254</v>
-      </c>
+      <c r="H6" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.24.255.254")</f>
+        <v>10.24.255.254</v>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
     </row>
-    <row r="7" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="7">
         <v>30</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="6" t="str">
         <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.34.0.0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>10.34.0.1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="6" t="str">
         <f t="shared" si="1"/>
         <v>10.34.0.1</v>
       </c>
-      <c r="H7" s="4" t="str">
-        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.33.255.254")</f>
-        <v>10.33.255.254</v>
-      </c>
+      <c r="H7" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.34.255.254")</f>
+        <v>10.34.255.254</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+    <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
     </row>
-    <row r="9" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
     </row>
-    <row r="10" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="6">
         <v>10</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
         <v>4.4.4.10</v>
       </c>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
     </row>
-    <row r="11" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="6">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
         <v>4.4.4.20</v>
       </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
     </row>
-    <row r="12" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="6">
         <v>30</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
         <v>4.4.4.30</v>
       </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
     </row>
-    <row r="14" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.14</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4" t="str">
+      <c r="E15" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
         <v>4.4.4.10</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="21">
         <v>10</v>
       </c>
-      <c r="I15" s="1" t="b" cm="1">
+      <c r="I15" s="21" t="b">
         <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="21"/>
     </row>
-    <row r="16" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="4" t="str">
+      <c r="C16" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.34</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="4" t="str">
+      <c r="E16" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
         <v>4.4.4.30</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="21">
         <v>30</v>
       </c>
-      <c r="I16" s="1" t="b" cm="1">
+      <c r="I16" s="21" t="b">
         <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
         <v>1</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="21"/>
     </row>
+    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEB0EB9-ED56-463C-A2D0-3C524DBED300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C60773-F857-43D2-8084-4B0102BE07ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="43">
   <si>
     <t>site</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>tunnel 30</t>
+  </si>
+  <si>
+    <t>antall-res</t>
+  </si>
+  <si>
+    <t>pri-1-10</t>
   </si>
 </sst>
 </file>
@@ -292,7 +298,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="144">
+  <dxfs count="154">
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
@@ -300,12 +312,174 @@
       <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -414,124 +588,40 @@
       <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -1149,127 +1239,103 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="16">
     <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="140"/>
-      <tableStyleElement type="headerRow" dxfId="143"/>
-      <tableStyleElement type="firstRowStripe" dxfId="142"/>
-      <tableStyleElement type="secondRowStripe" dxfId="141"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="153"/>
+      <tableStyleElement type="headerRow" dxfId="152"/>
+      <tableStyleElement type="firstRowStripe" dxfId="151"/>
+      <tableStyleElement type="secondRowStripe" dxfId="150"/>
     </tableStyle>
     <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="136"/>
-      <tableStyleElement type="headerRow" dxfId="139"/>
-      <tableStyleElement type="firstRowStripe" dxfId="138"/>
-      <tableStyleElement type="secondRowStripe" dxfId="137"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="149"/>
+      <tableStyleElement type="headerRow" dxfId="148"/>
+      <tableStyleElement type="firstRowStripe" dxfId="147"/>
+      <tableStyleElement type="secondRowStripe" dxfId="146"/>
     </tableStyle>
     <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="132"/>
-      <tableStyleElement type="headerRow" dxfId="135"/>
-      <tableStyleElement type="firstRowStripe" dxfId="134"/>
-      <tableStyleElement type="secondRowStripe" dxfId="133"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="145"/>
+      <tableStyleElement type="headerRow" dxfId="144"/>
+      <tableStyleElement type="firstRowStripe" dxfId="143"/>
+      <tableStyleElement type="secondRowStripe" dxfId="142"/>
     </tableStyle>
     <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="128"/>
-      <tableStyleElement type="headerRow" dxfId="131"/>
-      <tableStyleElement type="firstRowStripe" dxfId="130"/>
-      <tableStyleElement type="secondRowStripe" dxfId="129"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="141"/>
+      <tableStyleElement type="headerRow" dxfId="140"/>
+      <tableStyleElement type="firstRowStripe" dxfId="139"/>
+      <tableStyleElement type="secondRowStripe" dxfId="138"/>
     </tableStyle>
     <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="124"/>
-      <tableStyleElement type="headerRow" dxfId="127"/>
-      <tableStyleElement type="firstRowStripe" dxfId="126"/>
-      <tableStyleElement type="secondRowStripe" dxfId="125"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="137"/>
+      <tableStyleElement type="headerRow" dxfId="136"/>
+      <tableStyleElement type="firstRowStripe" dxfId="135"/>
+      <tableStyleElement type="secondRowStripe" dxfId="134"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="120"/>
-      <tableStyleElement type="headerRow" dxfId="123"/>
-      <tableStyleElement type="firstRowStripe" dxfId="122"/>
-      <tableStyleElement type="secondRowStripe" dxfId="121"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="133"/>
+      <tableStyleElement type="headerRow" dxfId="132"/>
+      <tableStyleElement type="firstRowStripe" dxfId="131"/>
+      <tableStyleElement type="secondRowStripe" dxfId="130"/>
     </tableStyle>
     <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="116"/>
-      <tableStyleElement type="headerRow" dxfId="119"/>
-      <tableStyleElement type="firstRowStripe" dxfId="118"/>
-      <tableStyleElement type="secondRowStripe" dxfId="117"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="129"/>
+      <tableStyleElement type="headerRow" dxfId="128"/>
+      <tableStyleElement type="firstRowStripe" dxfId="127"/>
+      <tableStyleElement type="secondRowStripe" dxfId="126"/>
     </tableStyle>
     <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="112"/>
-      <tableStyleElement type="headerRow" dxfId="115"/>
-      <tableStyleElement type="firstRowStripe" dxfId="114"/>
-      <tableStyleElement type="secondRowStripe" dxfId="113"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="125"/>
+      <tableStyleElement type="headerRow" dxfId="124"/>
+      <tableStyleElement type="firstRowStripe" dxfId="123"/>
+      <tableStyleElement type="secondRowStripe" dxfId="122"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="108"/>
-      <tableStyleElement type="headerRow" dxfId="111"/>
-      <tableStyleElement type="firstRowStripe" dxfId="110"/>
-      <tableStyleElement type="secondRowStripe" dxfId="109"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="121"/>
+      <tableStyleElement type="headerRow" dxfId="120"/>
+      <tableStyleElement type="firstRowStripe" dxfId="119"/>
+      <tableStyleElement type="secondRowStripe" dxfId="118"/>
     </tableStyle>
     <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="104"/>
-      <tableStyleElement type="headerRow" dxfId="107"/>
-      <tableStyleElement type="firstRowStripe" dxfId="106"/>
-      <tableStyleElement type="secondRowStripe" dxfId="105"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="117"/>
+      <tableStyleElement type="headerRow" dxfId="116"/>
+      <tableStyleElement type="firstRowStripe" dxfId="115"/>
+      <tableStyleElement type="secondRowStripe" dxfId="114"/>
     </tableStyle>
     <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
-      <tableStyleElement type="headerRow" dxfId="103"/>
-      <tableStyleElement type="firstRowStripe" dxfId="102"/>
-      <tableStyleElement type="secondRowStripe" dxfId="101"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="113"/>
+      <tableStyleElement type="headerRow" dxfId="112"/>
+      <tableStyleElement type="firstRowStripe" dxfId="111"/>
+      <tableStyleElement type="secondRowStripe" dxfId="110"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="96"/>
-      <tableStyleElement type="headerRow" dxfId="99"/>
-      <tableStyleElement type="firstRowStripe" dxfId="98"/>
-      <tableStyleElement type="secondRowStripe" dxfId="97"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="109"/>
+      <tableStyleElement type="headerRow" dxfId="108"/>
+      <tableStyleElement type="firstRowStripe" dxfId="107"/>
+      <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
     <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="92"/>
-      <tableStyleElement type="headerRow" dxfId="95"/>
-      <tableStyleElement type="firstRowStripe" dxfId="94"/>
-      <tableStyleElement type="secondRowStripe" dxfId="93"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="105"/>
+      <tableStyleElement type="headerRow" dxfId="104"/>
+      <tableStyleElement type="firstRowStripe" dxfId="103"/>
+      <tableStyleElement type="secondRowStripe" dxfId="102"/>
     </tableStyle>
     <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="88"/>
-      <tableStyleElement type="headerRow" dxfId="91"/>
-      <tableStyleElement type="firstRowStripe" dxfId="90"/>
-      <tableStyleElement type="secondRowStripe" dxfId="89"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="101"/>
+      <tableStyleElement type="headerRow" dxfId="100"/>
+      <tableStyleElement type="firstRowStripe" dxfId="99"/>
+      <tableStyleElement type="secondRowStripe" dxfId="98"/>
     </tableStyle>
     <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
-      <tableStyleElement type="headerRow" dxfId="87"/>
-      <tableStyleElement type="firstRowStripe" dxfId="86"/>
-      <tableStyleElement type="secondRowStripe" dxfId="85"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="97"/>
+      <tableStyleElement type="headerRow" dxfId="96"/>
+      <tableStyleElement type="firstRowStripe" dxfId="95"/>
+      <tableStyleElement type="secondRowStripe" dxfId="94"/>
     </tableStyle>
     <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="80"/>
-      <tableStyleElement type="headerRow" dxfId="83"/>
-      <tableStyleElement type="firstRowStripe" dxfId="82"/>
-      <tableStyleElement type="secondRowStripe" dxfId="81"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="93"/>
+      <tableStyleElement type="headerRow" dxfId="92"/>
+      <tableStyleElement type="firstRowStripe" dxfId="91"/>
+      <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1298,114 +1364,118 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell10" displayName="Tabell10" ref="A4:H7" headerRowDxfId="22" dataDxfId="20" totalsRowDxfId="21">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="vrf" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="vlan" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="interface" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="nett id" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="gateway" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="mask" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="address min" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="address max" dataDxfId="23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell10" displayName="Tabell10" ref="A4:J7" headerRowDxfId="80" dataDxfId="79" totalsRowDxfId="78">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="vrf" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="vlan" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="interface" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="nett id" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="gateway" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="mask" dataDxfId="72"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="address min" dataDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="address max" dataDxfId="70"/>
+    <tableColumn id="9" xr3:uid="{E31F8F39-D63F-4CA9-A605-F61B0B449EB7}" name="antall-res" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{872D007A-F188-416D-BDFA-5197C1FAB215}" name="pri-1-10" dataDxfId="3" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="Site 3-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabell11" displayName="Tabell11" ref="A9:D12" headerRowDxfId="15" dataDxfId="13" totalsRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabell11" displayName="Tabell11" ref="A9:D12" headerRowDxfId="69" dataDxfId="68" totalsRowDxfId="67">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="vrf" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="rt" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="loopback" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="laddr" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="vrf" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="rt" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="loopback" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="laddr" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="Site 3-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell12" displayName="Tabell12" ref="A14:J16" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell12" displayName="Tabell12" ref="A14:J16" headerRowDxfId="62" dataDxfId="61" totalsRowDxfId="60">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="tunnel id" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="vrf" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="ip address" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="mask" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="source" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="destination" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="gre mode" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="network-id" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="ipsec" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="ipsec key" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="tunnel id" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="vrf" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="ip address" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="mask" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="source" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="destination" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="gre mode" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="network-id" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="ipsec" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="ipsec key" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="Site 3-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Tabell13" displayName="Tabell13" ref="A1:F2" headerRowDxfId="73" dataDxfId="71" totalsRowDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Tabell13" displayName="Tabell13" ref="A1:F2" headerRowDxfId="49" dataDxfId="48" totalsRowDxfId="47">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="site" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="intf_prefix" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="router-id" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="brukernavn" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0C00-000005000000}" name="passord" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="vty_lines" dataDxfId="74"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="site" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="intf_prefix" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="router-id" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="brukernavn" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0C00-000005000000}" name="passord" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="vty_lines" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Tabell14" displayName="Tabell14" ref="A4:H7" headerRowDxfId="62" dataDxfId="60" totalsRowDxfId="61">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="vrf" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="vlan" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="interface" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="nett id" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="gateway" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="mask" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="address min" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0D00-000008000000}" name="address max" dataDxfId="63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Tabell14" displayName="Tabell14" ref="A4:J7" headerRowDxfId="40" dataDxfId="39" totalsRowDxfId="38">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="vrf" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="vlan" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="interface" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="nett id" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="gateway" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="mask" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="address min" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0D00-000008000000}" name="address max" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{D71A0F4B-8894-49C9-A19A-CB3D67B8C9A4}" name="antall-res" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{D72B4B49-342E-4472-A7DB-D9DD906E860B}" name="pri-1-10" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Tabell15" displayName="Tabell15" ref="A9:D12" headerRowDxfId="55" dataDxfId="53" totalsRowDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Tabell15" displayName="Tabell15" ref="A9:D12" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="vrf" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="rt" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="loopback" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0E00-000004000000}" name="laddr" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="vrf" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="rt" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="loopback" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0E00-000004000000}" name="laddr" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Tabell16" displayName="Tabell16" ref="A14:J16" headerRowDxfId="42" dataDxfId="40" totalsRowDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Tabell16" displayName="Tabell16" ref="A14:J16" headerRowDxfId="22" dataDxfId="21" totalsRowDxfId="20">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="tunnel id" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="vrf" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="ip address" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="mask" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="source" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="destination" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="gre mode" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="network-id" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="ipsec" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0F00-00000A000000}" name="ipsec key" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="tunnel id" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="vrf" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="ip address" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="mask" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="source" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="destination" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="gre mode" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="network-id" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="ipsec" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0F00-00000A000000}" name="ipsec key" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:H7">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:J7">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
@@ -1414,6 +1484,8 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-1-10"/>
   </tableColumns>
   <tableStyleInfo name="Site 1 (HUB)-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1464,8 +1536,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell2" displayName="Tabell2" ref="A4:H7">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell2" displayName="Tabell2" ref="A4:J7">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="interface"/>
@@ -1474,6 +1546,8 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-1-10"/>
   </tableColumns>
   <tableStyleInfo name="Site 2-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1510,14 +1584,14 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell9" displayName="Tabell9" ref="A1:F2" headerRowDxfId="33" dataDxfId="31" totalsRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell9" displayName="Tabell9" ref="A1:F2" headerRowDxfId="89" dataDxfId="88" totalsRowDxfId="87">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="intf_prefix" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="router-id" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="vty_lines" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="intf_prefix" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="router-id" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="vty_lines" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="Site 3-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1809,6 +1883,12 @@
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="I4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
@@ -1839,6 +1919,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.11.255.254")</f>
         <v>10.11.255.254</v>
       </c>
+      <c r="I5" s="6">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
@@ -1869,6 +1955,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.21.255.254")</f>
         <v>10.21.255.254</v>
       </c>
+      <c r="I6" s="6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -1898,6 +1990,12 @@
       <c r="H7" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.31.255.254")</f>
         <v>10.31.255.254</v>
+      </c>
+      <c r="I7" s="6">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3156,6 +3254,12 @@
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="I4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
@@ -3186,6 +3290,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.12.255.254")</f>
         <v>10.12.255.254</v>
       </c>
+      <c r="I5" s="6">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
@@ -3216,6 +3326,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.22.255.254")</f>
         <v>10.22.255.254</v>
       </c>
+      <c r="I6" s="6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -3245,6 +3361,12 @@
       <c r="H7" s="6" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.32.255.254")</f>
         <v>10.32.255.254</v>
+      </c>
+      <c r="I7" s="6">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4505,8 +4627,12 @@
       <c r="H4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="I4" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>42</v>
+      </c>
       <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4538,8 +4664,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.13.255.254")</f>
         <v>10.13.255.254</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
+      <c r="I5" s="16">
+        <v>10</v>
+      </c>
+      <c r="J5" s="11">
+        <v>5</v>
+      </c>
       <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4571,8 +4701,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.23.255.254")</f>
         <v>10.23.255.254</v>
       </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
+      <c r="I6" s="16">
+        <v>10</v>
+      </c>
+      <c r="J6" s="11">
+        <v>3</v>
+      </c>
       <c r="K6" s="11"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4604,8 +4738,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.33.255.254")</f>
         <v>10.33.255.254</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
+      <c r="I7" s="16">
+        <v>10</v>
+      </c>
+      <c r="J7" s="11">
+        <v>10</v>
+      </c>
       <c r="K7" s="11"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5932,8 +6070,12 @@
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
+      <c r="I4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
@@ -5964,8 +6106,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.14.255.254")</f>
         <v>10.14.255.254</v>
       </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
+      <c r="I5" s="6">
+        <v>10</v>
+      </c>
+      <c r="J5" s="20">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
@@ -5996,8 +6142,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.24.255.254")</f>
         <v>10.24.255.254</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="I6" s="6">
+        <v>10</v>
+      </c>
+      <c r="J6" s="20">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -6028,8 +6178,12 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.34.255.254")</f>
         <v>10.34.255.254</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="I7" s="6">
+        <v>10</v>
+      </c>
+      <c r="J7" s="20">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="22"/>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9CE4DE-73D7-4E1E-9669-2F7BDD07E822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC04455-DE09-4BB9-82E3-55A5CC03809B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
     <sheet name="Site 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Site 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="50">
   <si>
     <t>site</t>
   </si>
@@ -182,6 +183,9 @@
   <si>
     <t>pri-afxx</t>
   </si>
+  <si>
+    <t>30.1-20.4</t>
+  </si>
 </sst>
 </file>
 
@@ -276,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -322,17 +326,116 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="138">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1210,100 +1313,100 @@
   </dxfs>
   <tableStyles count="16">
     <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="112"/>
-      <tableStyleElement type="headerRow" dxfId="111"/>
-      <tableStyleElement type="firstRowStripe" dxfId="110"/>
-      <tableStyleElement type="secondRowStripe" dxfId="109"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="137"/>
+      <tableStyleElement type="headerRow" dxfId="136"/>
+      <tableStyleElement type="firstRowStripe" dxfId="135"/>
+      <tableStyleElement type="secondRowStripe" dxfId="134"/>
     </tableStyle>
     <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="108"/>
-      <tableStyleElement type="headerRow" dxfId="107"/>
-      <tableStyleElement type="firstRowStripe" dxfId="106"/>
-      <tableStyleElement type="secondRowStripe" dxfId="105"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="133"/>
+      <tableStyleElement type="headerRow" dxfId="132"/>
+      <tableStyleElement type="firstRowStripe" dxfId="131"/>
+      <tableStyleElement type="secondRowStripe" dxfId="130"/>
     </tableStyle>
     <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="104"/>
-      <tableStyleElement type="headerRow" dxfId="103"/>
-      <tableStyleElement type="firstRowStripe" dxfId="102"/>
-      <tableStyleElement type="secondRowStripe" dxfId="101"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="129"/>
+      <tableStyleElement type="headerRow" dxfId="128"/>
+      <tableStyleElement type="firstRowStripe" dxfId="127"/>
+      <tableStyleElement type="secondRowStripe" dxfId="126"/>
     </tableStyle>
     <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
-      <tableStyleElement type="headerRow" dxfId="99"/>
-      <tableStyleElement type="firstRowStripe" dxfId="98"/>
-      <tableStyleElement type="secondRowStripe" dxfId="97"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="125"/>
+      <tableStyleElement type="headerRow" dxfId="124"/>
+      <tableStyleElement type="firstRowStripe" dxfId="123"/>
+      <tableStyleElement type="secondRowStripe" dxfId="122"/>
     </tableStyle>
     <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="96"/>
-      <tableStyleElement type="headerRow" dxfId="95"/>
-      <tableStyleElement type="firstRowStripe" dxfId="94"/>
-      <tableStyleElement type="secondRowStripe" dxfId="93"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="121"/>
+      <tableStyleElement type="headerRow" dxfId="120"/>
+      <tableStyleElement type="firstRowStripe" dxfId="119"/>
+      <tableStyleElement type="secondRowStripe" dxfId="118"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="92"/>
-      <tableStyleElement type="headerRow" dxfId="91"/>
-      <tableStyleElement type="firstRowStripe" dxfId="90"/>
-      <tableStyleElement type="secondRowStripe" dxfId="89"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="117"/>
+      <tableStyleElement type="headerRow" dxfId="116"/>
+      <tableStyleElement type="firstRowStripe" dxfId="115"/>
+      <tableStyleElement type="secondRowStripe" dxfId="114"/>
     </tableStyle>
     <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="88"/>
-      <tableStyleElement type="headerRow" dxfId="87"/>
-      <tableStyleElement type="firstRowStripe" dxfId="86"/>
-      <tableStyleElement type="secondRowStripe" dxfId="85"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="113"/>
+      <tableStyleElement type="headerRow" dxfId="112"/>
+      <tableStyleElement type="firstRowStripe" dxfId="111"/>
+      <tableStyleElement type="secondRowStripe" dxfId="110"/>
     </tableStyle>
     <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
-      <tableStyleElement type="headerRow" dxfId="83"/>
-      <tableStyleElement type="firstRowStripe" dxfId="82"/>
-      <tableStyleElement type="secondRowStripe" dxfId="81"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="109"/>
+      <tableStyleElement type="headerRow" dxfId="108"/>
+      <tableStyleElement type="firstRowStripe" dxfId="107"/>
+      <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="80"/>
-      <tableStyleElement type="headerRow" dxfId="79"/>
-      <tableStyleElement type="firstRowStripe" dxfId="78"/>
-      <tableStyleElement type="secondRowStripe" dxfId="77"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="105"/>
+      <tableStyleElement type="headerRow" dxfId="104"/>
+      <tableStyleElement type="firstRowStripe" dxfId="103"/>
+      <tableStyleElement type="secondRowStripe" dxfId="102"/>
     </tableStyle>
     <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="76"/>
-      <tableStyleElement type="headerRow" dxfId="75"/>
-      <tableStyleElement type="firstRowStripe" dxfId="74"/>
-      <tableStyleElement type="secondRowStripe" dxfId="73"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="101"/>
+      <tableStyleElement type="headerRow" dxfId="100"/>
+      <tableStyleElement type="firstRowStripe" dxfId="99"/>
+      <tableStyleElement type="secondRowStripe" dxfId="98"/>
     </tableStyle>
     <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="72"/>
-      <tableStyleElement type="headerRow" dxfId="71"/>
-      <tableStyleElement type="firstRowStripe" dxfId="70"/>
-      <tableStyleElement type="secondRowStripe" dxfId="69"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="97"/>
+      <tableStyleElement type="headerRow" dxfId="96"/>
+      <tableStyleElement type="firstRowStripe" dxfId="95"/>
+      <tableStyleElement type="secondRowStripe" dxfId="94"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="68"/>
-      <tableStyleElement type="headerRow" dxfId="67"/>
-      <tableStyleElement type="firstRowStripe" dxfId="66"/>
-      <tableStyleElement type="secondRowStripe" dxfId="65"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="93"/>
+      <tableStyleElement type="headerRow" dxfId="92"/>
+      <tableStyleElement type="firstRowStripe" dxfId="91"/>
+      <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
     <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="64"/>
-      <tableStyleElement type="headerRow" dxfId="63"/>
-      <tableStyleElement type="firstRowStripe" dxfId="62"/>
-      <tableStyleElement type="secondRowStripe" dxfId="61"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="89"/>
+      <tableStyleElement type="headerRow" dxfId="88"/>
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
     <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="60"/>
-      <tableStyleElement type="headerRow" dxfId="59"/>
-      <tableStyleElement type="firstRowStripe" dxfId="58"/>
-      <tableStyleElement type="secondRowStripe" dxfId="57"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="85"/>
+      <tableStyleElement type="headerRow" dxfId="84"/>
+      <tableStyleElement type="firstRowStripe" dxfId="83"/>
+      <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
     <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="56"/>
-      <tableStyleElement type="headerRow" dxfId="55"/>
-      <tableStyleElement type="firstRowStripe" dxfId="54"/>
-      <tableStyleElement type="secondRowStripe" dxfId="53"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="81"/>
+      <tableStyleElement type="headerRow" dxfId="80"/>
+      <tableStyleElement type="firstRowStripe" dxfId="79"/>
+      <tableStyleElement type="secondRowStripe" dxfId="78"/>
     </tableStyle>
     <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="52"/>
-      <tableStyleElement type="headerRow" dxfId="51"/>
-      <tableStyleElement type="firstRowStripe" dxfId="50"/>
-      <tableStyleElement type="secondRowStripe" dxfId="49"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="77"/>
+      <tableStyleElement type="headerRow" dxfId="76"/>
+      <tableStyleElement type="firstRowStripe" dxfId="75"/>
+      <tableStyleElement type="secondRowStripe" dxfId="74"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1350,37 +1453,147 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="47" dataDxfId="46" totalsRowDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="72" dataDxfId="71" totalsRowDxfId="70">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="69">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="66" totalsRowDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{0D1C10A1-9717-4057-887E-5357402CB0E7}" name="Tabell1618242833" displayName="Tabell1618242833" ref="A21:I23" headerRowDxfId="39" dataDxfId="38" totalsRowDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{0D1C10A1-9717-4057-887E-5357402CB0E7}" name="Tabell1618242833" displayName="Tabell1618242833" ref="A21:I23" headerRowDxfId="64" dataDxfId="63" totalsRowDxfId="62">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{85F36277-7C1F-4D2C-A112-F88A589A07DE}" name="SW" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{5147590E-0FE4-463A-9241-58FBD204D8DE}" name="MGMT Vlan" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{F8B990D7-C517-482F-BAFB-8EA413932149}" name="MGMT ip" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{85F36277-7C1F-4D2C-A112-F88A589A07DE}" name="SW" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{5147590E-0FE4-463A-9241-58FBD204D8DE}" name="MGMT Vlan" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{F8B990D7-C517-482F-BAFB-8EA413932149}" name="MGMT ip" dataDxfId="59">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCAF6C67-3F43-4FFA-8105-4158589FBEBF}" name="gateway" dataDxfId="33">
+    <tableColumn id="4" xr3:uid="{BCAF6C67-3F43-4FFA-8105-4158589FBEBF}" name="gateway" dataDxfId="58">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D20CE737-A3E7-4538-BC2C-E8176E6D9EE6}" name="mask" dataDxfId="32">
+    <tableColumn id="5" xr3:uid="{D20CE737-A3E7-4538-BC2C-E8176E6D9EE6}" name="mask" dataDxfId="57">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9365541B-740A-44C6-ADF0-F56C3A9D13D1}" name="vlan-antall" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{7551B7F0-84D1-4CCD-9D8E-AEF551C0B4CA}" name="num_ports" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{7717CEDF-A842-4402-B477-8AD92D9C9A65}" name="intf_prefix" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{31DB8A8F-54E2-45C5-B25D-6C92CA4826D3}" name="num_port_ledig" dataDxfId="25" totalsRowDxfId="24">
+    <tableColumn id="6" xr3:uid="{9365541B-740A-44C6-ADF0-F56C3A9D13D1}" name="vlan-antall" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{7551B7F0-84D1-4CCD-9D8E-AEF551C0B4CA}" name="num_ports" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{7717CEDF-A842-4402-B477-8AD92D9C9A65}" name="intf_prefix" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{31DB8A8F-54E2-45C5-B25D-6C92CA4826D3}" name="num_port_ledig" dataDxfId="50" totalsRowDxfId="49">
+      <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6B700C0-B4F5-42B7-94D9-034E5D9D886A}" name="Tabell12" displayName="Tabell12" ref="A1:F2">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{E7B12A0B-F552-4AD1-B034-85DE8D128366}" name="site"/>
+    <tableColumn id="2" xr3:uid="{823F91E6-C232-4986-8B11-501983AB3D83}" name="intf_prefix"/>
+    <tableColumn id="3" xr3:uid="{1BB6D2AF-1EFB-4C0B-8B46-3A1E048E19A3}" name="router-id">
+      <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{DD52541D-0262-41F8-A0C2-C5F1AA0929D7}" name="brukernavn"/>
+    <tableColumn id="5" xr3:uid="{CDD9C4E3-0E8B-4E86-85C2-279123E643A3}" name="passord"/>
+    <tableColumn id="6" xr3:uid="{7F330FC1-3560-4A39-A3F8-03E4F41C54AE}" name="vty_lines"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{649ACA43-3D51-4804-81A7-64BC8A7E9622}" name="Tabell25" displayName="Tabell25" ref="A4:K7">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{CBD4B8CF-9CBE-47F2-B29A-B1AF1B0C3BB1}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{1906269D-C450-4F32-92EE-945DDC6448A8}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{B356E73D-3CCA-4BFB-87A1-40A712ECE9F9}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{16CF2537-CD91-4E4F-945A-47EE352162F5}" name="nett id"/>
+    <tableColumn id="5" xr3:uid="{98A5FF99-DA45-4181-BACD-B1DE22DAAF19}" name="gateway">
+      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{85C4E95C-9BB0-4DCC-BB74-C4F0C5D7507F}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{0E6F975A-960D-4569-B35D-1B3EA4B32E7E}" name="address min">
+      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{90B6F7A5-9BD7-49C1-B978-43855C69778B}" name="address max"/>
+    <tableColumn id="9" xr3:uid="{924908E3-556A-40DC-9275-15A17DCB79EE}" name="antall-res" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{06C63977-B34D-4B5A-A3DF-C4469BD779D7}" name="pri-afxx"/>
+    <tableColumn id="11" xr3:uid="{3BCA4967-58B4-4E19-8D6C-1D7A65EE09F2}" name="pri-1-10"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E32ED721-978A-4785-AA46-0077AED40AC5}" name="Tabell37" displayName="Tabell37" ref="A9:D12">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{A142F710-0A2E-4B21-A5B4-CF28E2CC91D0}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{12F08FF1-336D-484B-BC07-C46B0F20F4DB}" name="rt"/>
+    <tableColumn id="3" xr3:uid="{5F59AC8C-F391-4E41-A29E-32C2FC517FB6}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{6370F7E7-7FEB-45FA-9E15-EB12B0165106}" name="laddr"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{ABC57C07-BFFC-43E0-BADB-BE6B843826EE}" name="Tabell49" displayName="Tabell49" ref="A14:J16">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{3B50DDB7-93A8-47D0-9424-EAED219D7FA4}" name="tunnel id"/>
+    <tableColumn id="2" xr3:uid="{E62014BF-0F66-47D2-B038-DDF7CF024273}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{CA1B2AAB-E5BC-4D27-BDB0-53399772EDD8}" name="ip address"/>
+    <tableColumn id="4" xr3:uid="{1FE50572-5D46-47EE-9CAA-C5D7982C9A69}" name="mask"/>
+    <tableColumn id="5" xr3:uid="{857333EC-34C4-4CD6-AFE3-BF5BA353AE7F}" name="source"/>
+    <tableColumn id="6" xr3:uid="{4CB22131-CFD6-4C7D-8E78-FC39DAF37A9D}" name="destination"/>
+    <tableColumn id="7" xr3:uid="{15F438A3-5D0B-46E5-8019-48B1A494CE80}" name="gre mode"/>
+    <tableColumn id="8" xr3:uid="{DF369439-854E-4AA1-B3CD-7574E128DEDB}" name="network-id"/>
+    <tableColumn id="9" xr3:uid="{FB436501-7630-4736-B1B5-4BFF493C33BF}" name="ipsec">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{ED4C8B58-2EE3-4120-881F-1AA1DF5FA86E}" name="ipsec key"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BF23752F-BD82-401A-981D-B03F45E60744}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A18:D19" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{C10764F4-CFFC-4EE6-9EEA-82891DC993E3}" name="site" dataDxfId="20">
+      <calculatedColumnFormula>A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{495F2DCB-B8C1-4ED6-89E5-8F715B0716BB}" name="brukernavn" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{0AF6FD65-2F7E-47E7-AC42-98BED9837A14}" name="passord" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{817B17C3-5974-47D5-8903-3EB5C370F4C0}" name="vty_lines" dataDxfId="16" totalsRowDxfId="17"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{131BE48E-0BD4-4282-9346-3A5772CD50CB}" name="Tabell161824283312" displayName="Tabell161824283312" ref="A21:I23" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{72296002-AE4E-4E82-8305-4DDD12CA9BE2}" name="SW" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{2973A27B-3C31-4DE1-A0D7-9AC4974D229E}" name="MGMT Vlan" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{FBB420D8-ADD0-4632-A43B-10F32DF3105D}" name="MGMT ip" dataDxfId="10">
+      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{7D99B76D-9B56-49C4-9B59-4DED1EAF6B17}" name="gateway" dataDxfId="9">
+      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{E0CF3890-FEBD-4B81-ABF6-157ECCA5F3A4}" name="mask" dataDxfId="8">
+      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{4941A454-E75E-46D9-BD24-7C44A665D3F6}" name="vlan-antall" dataDxfId="6" totalsRowDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{08C93E9C-BB70-4A35-9AFF-1C123A3CD9A9}" name="num_ports" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{4BBEDCD8-9032-4F13-A138-6E836EDDF4D2}" name="intf_prefix" dataDxfId="2" totalsRowDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{2E94FBF2-04F2-4961-A5CD-DC3BCD091189}" name="num_port_ledig" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1399,7 +1612,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="48"/>
     <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{BBB41126-CDAD-40BD-92C3-0A8EEC64127E}" name="pri-1-10"/>
   </tableColumns>
@@ -1438,37 +1651,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="22" dataDxfId="21" totalsRowDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="47" dataDxfId="46" totalsRowDxfId="45">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="44">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" headerRowDxfId="40" dataDxfId="39" totalsRowDxfId="38">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="35">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="34">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="33">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="1" totalsRowDxfId="0">
+    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="26" totalsRowDxfId="25">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1501,7 +1714,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="73"/>
     <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{1CC9D42E-8B8D-4781-B4E6-7B024D0D4DB5}" name="pri-1-10"/>
   </tableColumns>
@@ -1723,16 +1936,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="6" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="6" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1752,7 +1965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1783,7 +1996,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -1818,7 +2031,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
@@ -1857,7 +2070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>19</v>
       </c>
@@ -1896,7 +2109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -1935,11 +2148,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -1953,7 +2166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1968,7 +2181,7 @@
         <v>1.1.1.10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -1983,7 +2196,7 @@
         <v>1.1.1.20</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
@@ -1998,8 +2211,8 @@
         <v>1.1.1.30</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
@@ -2031,7 +2244,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
@@ -2056,12 +2269,10 @@
       <c r="H15" s="2">
         <v>10</v>
       </c>
-      <c r="I15" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
@@ -2091,7 +2302,7 @@
       </c>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2100,7 +2311,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>0</v>
       </c>
@@ -2114,7 +2325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <f>A2</f>
         <v>1</v>
@@ -2129,8 +2340,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
@@ -2159,7 +2370,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>1</v>
       </c>
@@ -2192,984 +2403,984 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
@@ -3196,18 +3407,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:K994"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="6" width="12.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="6" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3227,7 +3438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -3258,7 +3469,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -3293,7 +3504,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
@@ -3332,7 +3543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>19</v>
       </c>
@@ -3371,7 +3582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -3410,11 +3621,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -3428,7 +3639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
@@ -3443,7 +3654,7 @@
         <v>2.2.2.10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -3458,7 +3669,7 @@
         <v>2.2.2.20</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
@@ -3473,8 +3684,8 @@
         <v>2.2.2.30</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
@@ -3506,7 +3717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
@@ -3531,13 +3742,13 @@
       <c r="H15" s="2">
         <v>10</v>
       </c>
-      <c r="I15" s="2" t="b">
+      <c r="I15" s="2">
         <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
@@ -3568,8 +3779,8 @@
       </c>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>0</v>
       </c>
@@ -3583,7 +3794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <f>A2</f>
         <v>2</v>
@@ -3598,8 +3809,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
@@ -3628,7 +3839,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>1</v>
       </c>
@@ -3640,7 +3851,7 @@
         <v>10.12.0.2</v>
       </c>
       <c r="D22" s="6" t="str">
-        <f t="shared" ref="D22:D23" si="3">$E$5</f>
+        <f t="shared" ref="D22" si="3">$E$5</f>
         <v>10.12.0.1</v>
       </c>
       <c r="E22" s="6" t="str">
@@ -3661,18 +3872,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>2</v>
       </c>
       <c r="B23" s="6">
         <v>10</v>
       </c>
-      <c r="C23" s="17" t="str">
+      <c r="C23" s="6" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
         <v>10.12.0.3</v>
       </c>
-      <c r="D23" s="17" t="str">
+      <c r="D23" s="6" t="str">
         <f>$E$5</f>
         <v>10.12.0.1</v>
       </c>
@@ -3689,982 +3900,982 @@
       <c r="H23" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="11">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F23" xr:uid="{25CC9412-61D9-442A-A712-97FD5AA60B1F}">
@@ -4682,4 +4893,518 @@
     <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83936876-D6BF-48B2-8128-D179264AEE99}">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.13.0.0</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="6" t="str">
+        <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="H5" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.12.255.254")</f>
+        <v>10.12.255.254</v>
+      </c>
+      <c r="I5" s="6">
+        <v>10</v>
+      </c>
+      <c r="J5" s="16">
+        <v>21</v>
+      </c>
+      <c r="K5" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="7">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="str">
+        <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.23.0.0</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>10.23.0.1</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>10.23.0.1</v>
+      </c>
+      <c r="H6" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.22.255.254")</f>
+        <v>10.22.255.254</v>
+      </c>
+      <c r="I6" s="6">
+        <v>10</v>
+      </c>
+      <c r="J6" s="16">
+        <v>11</v>
+      </c>
+      <c r="K6" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="7">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="str">
+        <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.33.0.0</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>10.33.0.1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>10.33.0.1</v>
+      </c>
+      <c r="H7" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.32.255.254")</f>
+        <v>10.32.255.254</v>
+      </c>
+      <c r="I7" s="6">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>41</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="6">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
+        <v>3.3.3.10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="6">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
+        <v>3.3.3.20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="6">
+        <v>30</v>
+      </c>
+      <c r="D12" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
+        <v>3.3.3.30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="6" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
+        <v>172.16.0.13</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
+        <v>3.3.3.10</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="6" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
+        <v>172.16.0.33</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
+        <v>3.3.3.30</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="2">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="b">
+        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <f>A2</f>
+        <v>3</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>1</v>
+      </c>
+      <c r="B22" s="6">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6" t="str">
+        <f t="shared" ref="C22" si="2">LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</f>
+        <v>10.13.0.2</v>
+      </c>
+      <c r="D22" s="6" t="str">
+        <f t="shared" ref="D22" si="3">$E$5</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="E22" s="6" t="str">
+        <f t="shared" ref="E22:E23" si="4">$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="11">
+        <v>10</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="11">
+        <f t="shared" ref="I22:I23" si="5">$G22-3</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>2</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
+        <v>10.13.0.3</v>
+      </c>
+      <c r="D23" s="6" t="str">
+        <f>$E$5</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="G23" s="11">
+        <v>4</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F23" xr:uid="{3B260FA1-AA62-4103-8C2D-5A08CBE85836}">
+      <formula1>IF(F22="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(F22,"-"),"."))&lt;=$G22-3)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="6">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC04455-DE09-4BB9-82E3-55A5CC03809B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D422DA-D1E2-4BF0-B67D-B73E42D50728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="52">
   <si>
     <t>site</t>
   </si>
@@ -186,6 +186,12 @@
   <si>
     <t>30.1-20.4</t>
   </si>
+  <si>
+    <t>isp_next_hop_addr</t>
+  </si>
+  <si>
+    <t>198.162.0.12</t>
+  </si>
 </sst>
 </file>
 
@@ -330,12 +336,30 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="138">
+  <dxfs count="139">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -497,6 +521,111 @@
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -566,111 +695,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -1313,100 +1337,100 @@
   </dxfs>
   <tableStyles count="16">
     <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="137"/>
-      <tableStyleElement type="headerRow" dxfId="136"/>
-      <tableStyleElement type="firstRowStripe" dxfId="135"/>
-      <tableStyleElement type="secondRowStripe" dxfId="134"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="138"/>
+      <tableStyleElement type="headerRow" dxfId="137"/>
+      <tableStyleElement type="firstRowStripe" dxfId="136"/>
+      <tableStyleElement type="secondRowStripe" dxfId="135"/>
     </tableStyle>
     <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="133"/>
-      <tableStyleElement type="headerRow" dxfId="132"/>
-      <tableStyleElement type="firstRowStripe" dxfId="131"/>
-      <tableStyleElement type="secondRowStripe" dxfId="130"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="134"/>
+      <tableStyleElement type="headerRow" dxfId="133"/>
+      <tableStyleElement type="firstRowStripe" dxfId="132"/>
+      <tableStyleElement type="secondRowStripe" dxfId="131"/>
     </tableStyle>
     <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="129"/>
-      <tableStyleElement type="headerRow" dxfId="128"/>
-      <tableStyleElement type="firstRowStripe" dxfId="127"/>
-      <tableStyleElement type="secondRowStripe" dxfId="126"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="130"/>
+      <tableStyleElement type="headerRow" dxfId="129"/>
+      <tableStyleElement type="firstRowStripe" dxfId="128"/>
+      <tableStyleElement type="secondRowStripe" dxfId="127"/>
     </tableStyle>
     <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="125"/>
-      <tableStyleElement type="headerRow" dxfId="124"/>
-      <tableStyleElement type="firstRowStripe" dxfId="123"/>
-      <tableStyleElement type="secondRowStripe" dxfId="122"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="126"/>
+      <tableStyleElement type="headerRow" dxfId="125"/>
+      <tableStyleElement type="firstRowStripe" dxfId="124"/>
+      <tableStyleElement type="secondRowStripe" dxfId="123"/>
     </tableStyle>
     <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="121"/>
-      <tableStyleElement type="headerRow" dxfId="120"/>
-      <tableStyleElement type="firstRowStripe" dxfId="119"/>
-      <tableStyleElement type="secondRowStripe" dxfId="118"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="122"/>
+      <tableStyleElement type="headerRow" dxfId="121"/>
+      <tableStyleElement type="firstRowStripe" dxfId="120"/>
+      <tableStyleElement type="secondRowStripe" dxfId="119"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="117"/>
-      <tableStyleElement type="headerRow" dxfId="116"/>
-      <tableStyleElement type="firstRowStripe" dxfId="115"/>
-      <tableStyleElement type="secondRowStripe" dxfId="114"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="118"/>
+      <tableStyleElement type="headerRow" dxfId="117"/>
+      <tableStyleElement type="firstRowStripe" dxfId="116"/>
+      <tableStyleElement type="secondRowStripe" dxfId="115"/>
     </tableStyle>
     <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="113"/>
-      <tableStyleElement type="headerRow" dxfId="112"/>
-      <tableStyleElement type="firstRowStripe" dxfId="111"/>
-      <tableStyleElement type="secondRowStripe" dxfId="110"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="114"/>
+      <tableStyleElement type="headerRow" dxfId="113"/>
+      <tableStyleElement type="firstRowStripe" dxfId="112"/>
+      <tableStyleElement type="secondRowStripe" dxfId="111"/>
     </tableStyle>
     <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="109"/>
-      <tableStyleElement type="headerRow" dxfId="108"/>
-      <tableStyleElement type="firstRowStripe" dxfId="107"/>
-      <tableStyleElement type="secondRowStripe" dxfId="106"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="110"/>
+      <tableStyleElement type="headerRow" dxfId="109"/>
+      <tableStyleElement type="firstRowStripe" dxfId="108"/>
+      <tableStyleElement type="secondRowStripe" dxfId="107"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="105"/>
-      <tableStyleElement type="headerRow" dxfId="104"/>
-      <tableStyleElement type="firstRowStripe" dxfId="103"/>
-      <tableStyleElement type="secondRowStripe" dxfId="102"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="106"/>
+      <tableStyleElement type="headerRow" dxfId="105"/>
+      <tableStyleElement type="firstRowStripe" dxfId="104"/>
+      <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
     <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="101"/>
-      <tableStyleElement type="headerRow" dxfId="100"/>
-      <tableStyleElement type="firstRowStripe" dxfId="99"/>
-      <tableStyleElement type="secondRowStripe" dxfId="98"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="102"/>
+      <tableStyleElement type="headerRow" dxfId="101"/>
+      <tableStyleElement type="firstRowStripe" dxfId="100"/>
+      <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
     <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="97"/>
-      <tableStyleElement type="headerRow" dxfId="96"/>
-      <tableStyleElement type="firstRowStripe" dxfId="95"/>
-      <tableStyleElement type="secondRowStripe" dxfId="94"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="98"/>
+      <tableStyleElement type="headerRow" dxfId="97"/>
+      <tableStyleElement type="firstRowStripe" dxfId="96"/>
+      <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="93"/>
-      <tableStyleElement type="headerRow" dxfId="92"/>
-      <tableStyleElement type="firstRowStripe" dxfId="91"/>
-      <tableStyleElement type="secondRowStripe" dxfId="90"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="94"/>
+      <tableStyleElement type="headerRow" dxfId="93"/>
+      <tableStyleElement type="firstRowStripe" dxfId="92"/>
+      <tableStyleElement type="secondRowStripe" dxfId="91"/>
     </tableStyle>
     <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="89"/>
-      <tableStyleElement type="headerRow" dxfId="88"/>
-      <tableStyleElement type="firstRowStripe" dxfId="87"/>
-      <tableStyleElement type="secondRowStripe" dxfId="86"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
+      <tableStyleElement type="headerRow" dxfId="89"/>
+      <tableStyleElement type="firstRowStripe" dxfId="88"/>
+      <tableStyleElement type="secondRowStripe" dxfId="87"/>
     </tableStyle>
     <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="85"/>
-      <tableStyleElement type="headerRow" dxfId="84"/>
-      <tableStyleElement type="firstRowStripe" dxfId="83"/>
-      <tableStyleElement type="secondRowStripe" dxfId="82"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="86"/>
+      <tableStyleElement type="headerRow" dxfId="85"/>
+      <tableStyleElement type="firstRowStripe" dxfId="84"/>
+      <tableStyleElement type="secondRowStripe" dxfId="83"/>
     </tableStyle>
     <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="81"/>
-      <tableStyleElement type="headerRow" dxfId="80"/>
-      <tableStyleElement type="firstRowStripe" dxfId="79"/>
-      <tableStyleElement type="secondRowStripe" dxfId="78"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="82"/>
+      <tableStyleElement type="headerRow" dxfId="81"/>
+      <tableStyleElement type="firstRowStripe" dxfId="80"/>
+      <tableStyleElement type="secondRowStripe" dxfId="79"/>
     </tableStyle>
     <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="77"/>
-      <tableStyleElement type="headerRow" dxfId="76"/>
-      <tableStyleElement type="firstRowStripe" dxfId="75"/>
-      <tableStyleElement type="secondRowStripe" dxfId="74"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
+      <tableStyleElement type="headerRow" dxfId="77"/>
+      <tableStyleElement type="firstRowStripe" dxfId="76"/>
+      <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1421,14 +1445,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:F2">
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:G2">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="router-id"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
+    <tableColumn id="7" xr3:uid="{317330A8-84F0-4160-B3DB-F31DCF020098}" name="isp_next_hop_addr" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Site 1 (HUB)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1453,37 +1478,37 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="72" dataDxfId="71" totalsRowDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="49" dataDxfId="48" totalsRowDxfId="47">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="69">
+    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="46">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="43" totalsRowDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{0D1C10A1-9717-4057-887E-5357402CB0E7}" name="Tabell1618242833" displayName="Tabell1618242833" ref="A21:I23" headerRowDxfId="64" dataDxfId="63" totalsRowDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{0D1C10A1-9717-4057-887E-5357402CB0E7}" name="Tabell1618242833" displayName="Tabell1618242833" ref="A21:I23" headerRowDxfId="41" dataDxfId="40" totalsRowDxfId="39">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{85F36277-7C1F-4D2C-A112-F88A589A07DE}" name="SW" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{5147590E-0FE4-463A-9241-58FBD204D8DE}" name="MGMT Vlan" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{F8B990D7-C517-482F-BAFB-8EA413932149}" name="MGMT ip" dataDxfId="59">
+    <tableColumn id="1" xr3:uid="{85F36277-7C1F-4D2C-A112-F88A589A07DE}" name="SW" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{5147590E-0FE4-463A-9241-58FBD204D8DE}" name="MGMT Vlan" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{F8B990D7-C517-482F-BAFB-8EA413932149}" name="MGMT ip" dataDxfId="36">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCAF6C67-3F43-4FFA-8105-4158589FBEBF}" name="gateway" dataDxfId="58">
+    <tableColumn id="4" xr3:uid="{BCAF6C67-3F43-4FFA-8105-4158589FBEBF}" name="gateway" dataDxfId="35">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D20CE737-A3E7-4538-BC2C-E8176E6D9EE6}" name="mask" dataDxfId="57">
+    <tableColumn id="5" xr3:uid="{D20CE737-A3E7-4538-BC2C-E8176E6D9EE6}" name="mask" dataDxfId="34">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9365541B-740A-44C6-ADF0-F56C3A9D13D1}" name="vlan-antall" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{7551B7F0-84D1-4CCD-9D8E-AEF551C0B4CA}" name="num_ports" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{7717CEDF-A842-4402-B477-8AD92D9C9A65}" name="intf_prefix" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{31DB8A8F-54E2-45C5-B25D-6C92CA4826D3}" name="num_port_ledig" dataDxfId="50" totalsRowDxfId="49">
+    <tableColumn id="6" xr3:uid="{9365541B-740A-44C6-ADF0-F56C3A9D13D1}" name="vlan-antall" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{7551B7F0-84D1-4CCD-9D8E-AEF551C0B4CA}" name="num_ports" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{7717CEDF-A842-4402-B477-8AD92D9C9A65}" name="intf_prefix" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{31DB8A8F-54E2-45C5-B25D-6C92CA4826D3}" name="num_port_ledig" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1522,7 +1547,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{90B6F7A5-9BD7-49C1-B978-43855C69778B}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{924908E3-556A-40DC-9275-15A17DCB79EE}" name="antall-res" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{924908E3-556A-40DC-9275-15A17DCB79EE}" name="antall-res" dataDxfId="25"/>
     <tableColumn id="10" xr3:uid="{06C63977-B34D-4B5A-A3DF-C4469BD779D7}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{3BCA4967-58B4-4E19-8D6C-1D7A65EE09F2}" name="pri-1-10"/>
   </tableColumns>
@@ -1563,37 +1588,37 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BF23752F-BD82-401A-981D-B03F45E60744}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A18:D19" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BF23752F-BD82-401A-981D-B03F45E60744}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A18:D19" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C10764F4-CFFC-4EE6-9EEA-82891DC993E3}" name="site" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{C10764F4-CFFC-4EE6-9EEA-82891DC993E3}" name="site" dataDxfId="21">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{495F2DCB-B8C1-4ED6-89E5-8F715B0716BB}" name="brukernavn" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{0AF6FD65-2F7E-47E7-AC42-98BED9837A14}" name="passord" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{817B17C3-5974-47D5-8903-3EB5C370F4C0}" name="vty_lines" dataDxfId="16" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{495F2DCB-B8C1-4ED6-89E5-8F715B0716BB}" name="brukernavn" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{0AF6FD65-2F7E-47E7-AC42-98BED9837A14}" name="passord" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{817B17C3-5974-47D5-8903-3EB5C370F4C0}" name="vty_lines" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{131BE48E-0BD4-4282-9346-3A5772CD50CB}" name="Tabell161824283312" displayName="Tabell161824283312" ref="A21:I23" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{131BE48E-0BD4-4282-9346-3A5772CD50CB}" name="Tabell161824283312" displayName="Tabell161824283312" ref="A21:I23" headerRowDxfId="16" dataDxfId="15" totalsRowDxfId="14">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{72296002-AE4E-4E82-8305-4DDD12CA9BE2}" name="SW" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{2973A27B-3C31-4DE1-A0D7-9AC4974D229E}" name="MGMT Vlan" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{FBB420D8-ADD0-4632-A43B-10F32DF3105D}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{72296002-AE4E-4E82-8305-4DDD12CA9BE2}" name="SW" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{2973A27B-3C31-4DE1-A0D7-9AC4974D229E}" name="MGMT Vlan" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{FBB420D8-ADD0-4632-A43B-10F32DF3105D}" name="MGMT ip" dataDxfId="11">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7D99B76D-9B56-49C4-9B59-4DED1EAF6B17}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{7D99B76D-9B56-49C4-9B59-4DED1EAF6B17}" name="gateway" dataDxfId="10">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E0CF3890-FEBD-4B81-ABF6-157ECCA5F3A4}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{E0CF3890-FEBD-4B81-ABF6-157ECCA5F3A4}" name="mask" dataDxfId="9">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4941A454-E75E-46D9-BD24-7C44A665D3F6}" name="vlan-antall" dataDxfId="6" totalsRowDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{08C93E9C-BB70-4A35-9AFF-1C123A3CD9A9}" name="num_ports" dataDxfId="4" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{4BBEDCD8-9032-4F13-A138-6E836EDDF4D2}" name="intf_prefix" dataDxfId="2" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{2E94FBF2-04F2-4961-A5CD-DC3BCD091189}" name="num_port_ledig" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="6" xr3:uid="{4941A454-E75E-46D9-BD24-7C44A665D3F6}" name="vlan-antall" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{08C93E9C-BB70-4A35-9AFF-1C123A3CD9A9}" name="num_ports" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{4BBEDCD8-9032-4F13-A138-6E836EDDF4D2}" name="intf_prefix" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{2E94FBF2-04F2-4961-A5CD-DC3BCD091189}" name="num_port_ledig" dataDxfId="2" totalsRowDxfId="1">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1612,7 +1637,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="74"/>
     <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{BBB41126-CDAD-40BD-92C3-0A8EEC64127E}" name="pri-1-10"/>
   </tableColumns>
@@ -1651,37 +1676,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="47" dataDxfId="46" totalsRowDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="73" dataDxfId="72" totalsRowDxfId="71">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="70">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" headerRowDxfId="40" dataDxfId="39" totalsRowDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" headerRowDxfId="66" dataDxfId="65" totalsRowDxfId="64">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="61">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="60">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="59">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="26" totalsRowDxfId="25">
+    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="52" totalsRowDxfId="51">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1714,7 +1739,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="50"/>
     <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{1CC9D42E-8B8D-4781-B4E6-7B024D0D4DB5}" name="pri-1-10"/>
   </tableColumns>
@@ -1942,6 +1967,7 @@
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
     <col min="3" max="4" width="23.88671875" customWidth="1"/>
     <col min="5" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" customWidth="1"/>
     <col min="9" max="9" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1964,6 +1990,9 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
@@ -1984,6 +2013,9 @@
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5358,7 +5390,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>2</v>
       </c>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D422DA-D1E2-4BF0-B67D-B73E42D50728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F3C545-E422-41E8-BD17-30F4FBE8979C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="50">
   <si>
     <t>site</t>
   </si>
@@ -186,12 +186,6 @@
   <si>
     <t>30.1-20.4</t>
   </si>
-  <si>
-    <t>isp_next_hop_addr</t>
-  </si>
-  <si>
-    <t>198.162.0.12</t>
-  </si>
 </sst>
 </file>
 
@@ -336,25 +330,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="139">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="138">
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1337,100 +1313,100 @@
   </dxfs>
   <tableStyles count="16">
     <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="138"/>
-      <tableStyleElement type="headerRow" dxfId="137"/>
-      <tableStyleElement type="firstRowStripe" dxfId="136"/>
-      <tableStyleElement type="secondRowStripe" dxfId="135"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="137"/>
+      <tableStyleElement type="headerRow" dxfId="136"/>
+      <tableStyleElement type="firstRowStripe" dxfId="135"/>
+      <tableStyleElement type="secondRowStripe" dxfId="134"/>
     </tableStyle>
     <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="134"/>
-      <tableStyleElement type="headerRow" dxfId="133"/>
-      <tableStyleElement type="firstRowStripe" dxfId="132"/>
-      <tableStyleElement type="secondRowStripe" dxfId="131"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="133"/>
+      <tableStyleElement type="headerRow" dxfId="132"/>
+      <tableStyleElement type="firstRowStripe" dxfId="131"/>
+      <tableStyleElement type="secondRowStripe" dxfId="130"/>
     </tableStyle>
     <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="130"/>
-      <tableStyleElement type="headerRow" dxfId="129"/>
-      <tableStyleElement type="firstRowStripe" dxfId="128"/>
-      <tableStyleElement type="secondRowStripe" dxfId="127"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="129"/>
+      <tableStyleElement type="headerRow" dxfId="128"/>
+      <tableStyleElement type="firstRowStripe" dxfId="127"/>
+      <tableStyleElement type="secondRowStripe" dxfId="126"/>
     </tableStyle>
     <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="126"/>
-      <tableStyleElement type="headerRow" dxfId="125"/>
-      <tableStyleElement type="firstRowStripe" dxfId="124"/>
-      <tableStyleElement type="secondRowStripe" dxfId="123"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="125"/>
+      <tableStyleElement type="headerRow" dxfId="124"/>
+      <tableStyleElement type="firstRowStripe" dxfId="123"/>
+      <tableStyleElement type="secondRowStripe" dxfId="122"/>
     </tableStyle>
     <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="122"/>
-      <tableStyleElement type="headerRow" dxfId="121"/>
-      <tableStyleElement type="firstRowStripe" dxfId="120"/>
-      <tableStyleElement type="secondRowStripe" dxfId="119"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="121"/>
+      <tableStyleElement type="headerRow" dxfId="120"/>
+      <tableStyleElement type="firstRowStripe" dxfId="119"/>
+      <tableStyleElement type="secondRowStripe" dxfId="118"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="118"/>
-      <tableStyleElement type="headerRow" dxfId="117"/>
-      <tableStyleElement type="firstRowStripe" dxfId="116"/>
-      <tableStyleElement type="secondRowStripe" dxfId="115"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="117"/>
+      <tableStyleElement type="headerRow" dxfId="116"/>
+      <tableStyleElement type="firstRowStripe" dxfId="115"/>
+      <tableStyleElement type="secondRowStripe" dxfId="114"/>
     </tableStyle>
     <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="114"/>
-      <tableStyleElement type="headerRow" dxfId="113"/>
-      <tableStyleElement type="firstRowStripe" dxfId="112"/>
-      <tableStyleElement type="secondRowStripe" dxfId="111"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="113"/>
+      <tableStyleElement type="headerRow" dxfId="112"/>
+      <tableStyleElement type="firstRowStripe" dxfId="111"/>
+      <tableStyleElement type="secondRowStripe" dxfId="110"/>
     </tableStyle>
     <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="110"/>
-      <tableStyleElement type="headerRow" dxfId="109"/>
-      <tableStyleElement type="firstRowStripe" dxfId="108"/>
-      <tableStyleElement type="secondRowStripe" dxfId="107"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="109"/>
+      <tableStyleElement type="headerRow" dxfId="108"/>
+      <tableStyleElement type="firstRowStripe" dxfId="107"/>
+      <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="106"/>
-      <tableStyleElement type="headerRow" dxfId="105"/>
-      <tableStyleElement type="firstRowStripe" dxfId="104"/>
-      <tableStyleElement type="secondRowStripe" dxfId="103"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="105"/>
+      <tableStyleElement type="headerRow" dxfId="104"/>
+      <tableStyleElement type="firstRowStripe" dxfId="103"/>
+      <tableStyleElement type="secondRowStripe" dxfId="102"/>
     </tableStyle>
     <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="102"/>
-      <tableStyleElement type="headerRow" dxfId="101"/>
-      <tableStyleElement type="firstRowStripe" dxfId="100"/>
-      <tableStyleElement type="secondRowStripe" dxfId="99"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="101"/>
+      <tableStyleElement type="headerRow" dxfId="100"/>
+      <tableStyleElement type="firstRowStripe" dxfId="99"/>
+      <tableStyleElement type="secondRowStripe" dxfId="98"/>
     </tableStyle>
     <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="98"/>
-      <tableStyleElement type="headerRow" dxfId="97"/>
-      <tableStyleElement type="firstRowStripe" dxfId="96"/>
-      <tableStyleElement type="secondRowStripe" dxfId="95"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="97"/>
+      <tableStyleElement type="headerRow" dxfId="96"/>
+      <tableStyleElement type="firstRowStripe" dxfId="95"/>
+      <tableStyleElement type="secondRowStripe" dxfId="94"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="94"/>
-      <tableStyleElement type="headerRow" dxfId="93"/>
-      <tableStyleElement type="firstRowStripe" dxfId="92"/>
-      <tableStyleElement type="secondRowStripe" dxfId="91"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="93"/>
+      <tableStyleElement type="headerRow" dxfId="92"/>
+      <tableStyleElement type="firstRowStripe" dxfId="91"/>
+      <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
     <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
-      <tableStyleElement type="headerRow" dxfId="89"/>
-      <tableStyleElement type="firstRowStripe" dxfId="88"/>
-      <tableStyleElement type="secondRowStripe" dxfId="87"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="89"/>
+      <tableStyleElement type="headerRow" dxfId="88"/>
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
     <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="86"/>
-      <tableStyleElement type="headerRow" dxfId="85"/>
-      <tableStyleElement type="firstRowStripe" dxfId="84"/>
-      <tableStyleElement type="secondRowStripe" dxfId="83"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="85"/>
+      <tableStyleElement type="headerRow" dxfId="84"/>
+      <tableStyleElement type="firstRowStripe" dxfId="83"/>
+      <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
     <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="82"/>
-      <tableStyleElement type="headerRow" dxfId="81"/>
-      <tableStyleElement type="firstRowStripe" dxfId="80"/>
-      <tableStyleElement type="secondRowStripe" dxfId="79"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="81"/>
+      <tableStyleElement type="headerRow" dxfId="80"/>
+      <tableStyleElement type="firstRowStripe" dxfId="79"/>
+      <tableStyleElement type="secondRowStripe" dxfId="78"/>
     </tableStyle>
     <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
-      <tableStyleElement type="headerRow" dxfId="77"/>
-      <tableStyleElement type="firstRowStripe" dxfId="76"/>
-      <tableStyleElement type="secondRowStripe" dxfId="75"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="77"/>
+      <tableStyleElement type="headerRow" dxfId="76"/>
+      <tableStyleElement type="firstRowStripe" dxfId="75"/>
+      <tableStyleElement type="secondRowStripe" dxfId="74"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1445,15 +1421,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:G2">
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:F2">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="router-id"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{317330A8-84F0-4160-B3DB-F31DCF020098}" name="isp_next_hop_addr" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Site 1 (HUB)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1478,37 +1453,37 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="49" dataDxfId="48" totalsRowDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="48" dataDxfId="47" totalsRowDxfId="46">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="45">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="42" totalsRowDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{0D1C10A1-9717-4057-887E-5357402CB0E7}" name="Tabell1618242833" displayName="Tabell1618242833" ref="A21:I23" headerRowDxfId="41" dataDxfId="40" totalsRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{0D1C10A1-9717-4057-887E-5357402CB0E7}" name="Tabell1618242833" displayName="Tabell1618242833" ref="A21:I23" headerRowDxfId="40" dataDxfId="39" totalsRowDxfId="38">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{85F36277-7C1F-4D2C-A112-F88A589A07DE}" name="SW" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{5147590E-0FE4-463A-9241-58FBD204D8DE}" name="MGMT Vlan" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{F8B990D7-C517-482F-BAFB-8EA413932149}" name="MGMT ip" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{85F36277-7C1F-4D2C-A112-F88A589A07DE}" name="SW" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{5147590E-0FE4-463A-9241-58FBD204D8DE}" name="MGMT Vlan" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{F8B990D7-C517-482F-BAFB-8EA413932149}" name="MGMT ip" dataDxfId="35">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCAF6C67-3F43-4FFA-8105-4158589FBEBF}" name="gateway" dataDxfId="35">
+    <tableColumn id="4" xr3:uid="{BCAF6C67-3F43-4FFA-8105-4158589FBEBF}" name="gateway" dataDxfId="34">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D20CE737-A3E7-4538-BC2C-E8176E6D9EE6}" name="mask" dataDxfId="34">
+    <tableColumn id="5" xr3:uid="{D20CE737-A3E7-4538-BC2C-E8176E6D9EE6}" name="mask" dataDxfId="33">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9365541B-740A-44C6-ADF0-F56C3A9D13D1}" name="vlan-antall" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{7551B7F0-84D1-4CCD-9D8E-AEF551C0B4CA}" name="num_ports" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{7717CEDF-A842-4402-B477-8AD92D9C9A65}" name="intf_prefix" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{31DB8A8F-54E2-45C5-B25D-6C92CA4826D3}" name="num_port_ledig" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="6" xr3:uid="{9365541B-740A-44C6-ADF0-F56C3A9D13D1}" name="vlan-antall" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{7551B7F0-84D1-4CCD-9D8E-AEF551C0B4CA}" name="num_ports" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{7717CEDF-A842-4402-B477-8AD92D9C9A65}" name="intf_prefix" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{31DB8A8F-54E2-45C5-B25D-6C92CA4826D3}" name="num_port_ledig" dataDxfId="26" totalsRowDxfId="25">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1547,7 +1522,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{90B6F7A5-9BD7-49C1-B978-43855C69778B}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{924908E3-556A-40DC-9275-15A17DCB79EE}" name="antall-res" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{924908E3-556A-40DC-9275-15A17DCB79EE}" name="antall-res" dataDxfId="24"/>
     <tableColumn id="10" xr3:uid="{06C63977-B34D-4B5A-A3DF-C4469BD779D7}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{3BCA4967-58B4-4E19-8D6C-1D7A65EE09F2}" name="pri-1-10"/>
   </tableColumns>
@@ -1588,37 +1563,37 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BF23752F-BD82-401A-981D-B03F45E60744}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A18:D19" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BF23752F-BD82-401A-981D-B03F45E60744}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A18:D19" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C10764F4-CFFC-4EE6-9EEA-82891DC993E3}" name="site" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{C10764F4-CFFC-4EE6-9EEA-82891DC993E3}" name="site" dataDxfId="20">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{495F2DCB-B8C1-4ED6-89E5-8F715B0716BB}" name="brukernavn" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{0AF6FD65-2F7E-47E7-AC42-98BED9837A14}" name="passord" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{817B17C3-5974-47D5-8903-3EB5C370F4C0}" name="vty_lines" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{495F2DCB-B8C1-4ED6-89E5-8F715B0716BB}" name="brukernavn" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{0AF6FD65-2F7E-47E7-AC42-98BED9837A14}" name="passord" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{817B17C3-5974-47D5-8903-3EB5C370F4C0}" name="vty_lines" dataDxfId="17" totalsRowDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{131BE48E-0BD4-4282-9346-3A5772CD50CB}" name="Tabell161824283312" displayName="Tabell161824283312" ref="A21:I23" headerRowDxfId="16" dataDxfId="15" totalsRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{131BE48E-0BD4-4282-9346-3A5772CD50CB}" name="Tabell161824283312" displayName="Tabell161824283312" ref="A21:I23" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{72296002-AE4E-4E82-8305-4DDD12CA9BE2}" name="SW" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{2973A27B-3C31-4DE1-A0D7-9AC4974D229E}" name="MGMT Vlan" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{FBB420D8-ADD0-4632-A43B-10F32DF3105D}" name="MGMT ip" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{72296002-AE4E-4E82-8305-4DDD12CA9BE2}" name="SW" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{2973A27B-3C31-4DE1-A0D7-9AC4974D229E}" name="MGMT Vlan" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{FBB420D8-ADD0-4632-A43B-10F32DF3105D}" name="MGMT ip" dataDxfId="10">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7D99B76D-9B56-49C4-9B59-4DED1EAF6B17}" name="gateway" dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{7D99B76D-9B56-49C4-9B59-4DED1EAF6B17}" name="gateway" dataDxfId="9">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E0CF3890-FEBD-4B81-ABF6-157ECCA5F3A4}" name="mask" dataDxfId="9">
+    <tableColumn id="5" xr3:uid="{E0CF3890-FEBD-4B81-ABF6-157ECCA5F3A4}" name="mask" dataDxfId="8">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4941A454-E75E-46D9-BD24-7C44A665D3F6}" name="vlan-antall" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{08C93E9C-BB70-4A35-9AFF-1C123A3CD9A9}" name="num_ports" dataDxfId="6" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{4BBEDCD8-9032-4F13-A138-6E836EDDF4D2}" name="intf_prefix" dataDxfId="4" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{2E94FBF2-04F2-4961-A5CD-DC3BCD091189}" name="num_port_ledig" dataDxfId="2" totalsRowDxfId="1">
+    <tableColumn id="6" xr3:uid="{4941A454-E75E-46D9-BD24-7C44A665D3F6}" name="vlan-antall" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{08C93E9C-BB70-4A35-9AFF-1C123A3CD9A9}" name="num_ports" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{4BBEDCD8-9032-4F13-A138-6E836EDDF4D2}" name="intf_prefix" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{2E94FBF2-04F2-4961-A5CD-DC3BCD091189}" name="num_port_ledig" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1637,7 +1612,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="73"/>
     <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{BBB41126-CDAD-40BD-92C3-0A8EEC64127E}" name="pri-1-10"/>
   </tableColumns>
@@ -1676,37 +1651,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="73" dataDxfId="72" totalsRowDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="72" dataDxfId="71" totalsRowDxfId="70">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="70">
+    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="69">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" headerRowDxfId="66" dataDxfId="65" totalsRowDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" headerRowDxfId="65" dataDxfId="64" totalsRowDxfId="63">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="60">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="60">
+    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="59">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="59">
+    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="58">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="52" totalsRowDxfId="51">
+    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="53" totalsRowDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="51" totalsRowDxfId="50">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1739,7 +1714,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="49"/>
     <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{1CC9D42E-8B8D-4781-B4E6-7B024D0D4DB5}" name="pri-1-10"/>
   </tableColumns>
@@ -1990,9 +1965,6 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
@@ -2013,9 +1985,6 @@
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4FB680-C061-4FAC-AA77-E5AEE21A30C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575F4A5D-A441-4C0F-800A-E462E8EED511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="51">
   <si>
     <t>site</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t>pri-afxx</t>
+  </si>
+  <si>
+    <t>30.2-20.5</t>
+  </si>
+  <si>
+    <t>20.1-10.1</t>
   </si>
 </sst>
 </file>
@@ -276,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -319,35 +325,41 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="113">
-    <dxf>
+  <dxfs count="111">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -363,14 +375,83 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="11"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -442,49 +523,10 @@
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1201,100 +1243,100 @@
   </dxfs>
   <tableStyles count="16">
     <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="112"/>
-      <tableStyleElement type="headerRow" dxfId="111"/>
-      <tableStyleElement type="firstRowStripe" dxfId="110"/>
-      <tableStyleElement type="secondRowStripe" dxfId="109"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="110"/>
+      <tableStyleElement type="headerRow" dxfId="109"/>
+      <tableStyleElement type="firstRowStripe" dxfId="108"/>
+      <tableStyleElement type="secondRowStripe" dxfId="107"/>
     </tableStyle>
     <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="108"/>
-      <tableStyleElement type="headerRow" dxfId="107"/>
-      <tableStyleElement type="firstRowStripe" dxfId="106"/>
-      <tableStyleElement type="secondRowStripe" dxfId="105"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="106"/>
+      <tableStyleElement type="headerRow" dxfId="105"/>
+      <tableStyleElement type="firstRowStripe" dxfId="104"/>
+      <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
     <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="104"/>
-      <tableStyleElement type="headerRow" dxfId="103"/>
-      <tableStyleElement type="firstRowStripe" dxfId="102"/>
-      <tableStyleElement type="secondRowStripe" dxfId="101"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="102"/>
+      <tableStyleElement type="headerRow" dxfId="101"/>
+      <tableStyleElement type="firstRowStripe" dxfId="100"/>
+      <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
     <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
-      <tableStyleElement type="headerRow" dxfId="99"/>
-      <tableStyleElement type="firstRowStripe" dxfId="98"/>
-      <tableStyleElement type="secondRowStripe" dxfId="97"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="98"/>
+      <tableStyleElement type="headerRow" dxfId="97"/>
+      <tableStyleElement type="firstRowStripe" dxfId="96"/>
+      <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
     <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="96"/>
-      <tableStyleElement type="headerRow" dxfId="95"/>
-      <tableStyleElement type="firstRowStripe" dxfId="94"/>
-      <tableStyleElement type="secondRowStripe" dxfId="93"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="94"/>
+      <tableStyleElement type="headerRow" dxfId="93"/>
+      <tableStyleElement type="firstRowStripe" dxfId="92"/>
+      <tableStyleElement type="secondRowStripe" dxfId="91"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="92"/>
-      <tableStyleElement type="headerRow" dxfId="91"/>
-      <tableStyleElement type="firstRowStripe" dxfId="90"/>
-      <tableStyleElement type="secondRowStripe" dxfId="89"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
+      <tableStyleElement type="headerRow" dxfId="89"/>
+      <tableStyleElement type="firstRowStripe" dxfId="88"/>
+      <tableStyleElement type="secondRowStripe" dxfId="87"/>
     </tableStyle>
     <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="88"/>
-      <tableStyleElement type="headerRow" dxfId="87"/>
-      <tableStyleElement type="firstRowStripe" dxfId="86"/>
-      <tableStyleElement type="secondRowStripe" dxfId="85"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="86"/>
+      <tableStyleElement type="headerRow" dxfId="85"/>
+      <tableStyleElement type="firstRowStripe" dxfId="84"/>
+      <tableStyleElement type="secondRowStripe" dxfId="83"/>
     </tableStyle>
     <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
-      <tableStyleElement type="headerRow" dxfId="83"/>
-      <tableStyleElement type="firstRowStripe" dxfId="82"/>
-      <tableStyleElement type="secondRowStripe" dxfId="81"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="82"/>
+      <tableStyleElement type="headerRow" dxfId="81"/>
+      <tableStyleElement type="firstRowStripe" dxfId="80"/>
+      <tableStyleElement type="secondRowStripe" dxfId="79"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="80"/>
-      <tableStyleElement type="headerRow" dxfId="79"/>
-      <tableStyleElement type="firstRowStripe" dxfId="78"/>
-      <tableStyleElement type="secondRowStripe" dxfId="77"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
+      <tableStyleElement type="headerRow" dxfId="77"/>
+      <tableStyleElement type="firstRowStripe" dxfId="76"/>
+      <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
     <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="76"/>
-      <tableStyleElement type="headerRow" dxfId="75"/>
-      <tableStyleElement type="firstRowStripe" dxfId="74"/>
-      <tableStyleElement type="secondRowStripe" dxfId="73"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="74"/>
+      <tableStyleElement type="headerRow" dxfId="73"/>
+      <tableStyleElement type="firstRowStripe" dxfId="72"/>
+      <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
     <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="72"/>
-      <tableStyleElement type="headerRow" dxfId="71"/>
-      <tableStyleElement type="firstRowStripe" dxfId="70"/>
-      <tableStyleElement type="secondRowStripe" dxfId="69"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="70"/>
+      <tableStyleElement type="headerRow" dxfId="69"/>
+      <tableStyleElement type="firstRowStripe" dxfId="68"/>
+      <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="68"/>
-      <tableStyleElement type="headerRow" dxfId="67"/>
-      <tableStyleElement type="firstRowStripe" dxfId="66"/>
-      <tableStyleElement type="secondRowStripe" dxfId="65"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="66"/>
+      <tableStyleElement type="headerRow" dxfId="65"/>
+      <tableStyleElement type="firstRowStripe" dxfId="64"/>
+      <tableStyleElement type="secondRowStripe" dxfId="63"/>
     </tableStyle>
     <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="64"/>
-      <tableStyleElement type="headerRow" dxfId="63"/>
-      <tableStyleElement type="firstRowStripe" dxfId="62"/>
-      <tableStyleElement type="secondRowStripe" dxfId="61"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="62"/>
+      <tableStyleElement type="headerRow" dxfId="61"/>
+      <tableStyleElement type="firstRowStripe" dxfId="60"/>
+      <tableStyleElement type="secondRowStripe" dxfId="59"/>
     </tableStyle>
     <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="60"/>
-      <tableStyleElement type="headerRow" dxfId="59"/>
-      <tableStyleElement type="firstRowStripe" dxfId="58"/>
-      <tableStyleElement type="secondRowStripe" dxfId="57"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="58"/>
+      <tableStyleElement type="headerRow" dxfId="57"/>
+      <tableStyleElement type="firstRowStripe" dxfId="56"/>
+      <tableStyleElement type="secondRowStripe" dxfId="55"/>
     </tableStyle>
     <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="56"/>
-      <tableStyleElement type="headerRow" dxfId="55"/>
-      <tableStyleElement type="firstRowStripe" dxfId="54"/>
-      <tableStyleElement type="secondRowStripe" dxfId="53"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="54"/>
+      <tableStyleElement type="headerRow" dxfId="53"/>
+      <tableStyleElement type="firstRowStripe" dxfId="52"/>
+      <tableStyleElement type="secondRowStripe" dxfId="51"/>
     </tableStyle>
     <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="52"/>
-      <tableStyleElement type="headerRow" dxfId="51"/>
-      <tableStyleElement type="firstRowStripe" dxfId="50"/>
-      <tableStyleElement type="secondRowStripe" dxfId="49"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="50"/>
+      <tableStyleElement type="headerRow" dxfId="49"/>
+      <tableStyleElement type="firstRowStripe" dxfId="48"/>
+      <tableStyleElement type="secondRowStripe" dxfId="47"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1341,37 +1383,39 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="33" dataDxfId="32" totalsRowDxfId="31">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="30">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="27" totalsRowDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I22" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I24" headerRowDxfId="23" totalsRowDxfId="22">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="8">
+      <calculatedColumnFormula>ROW()-21</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" dataDxfId="6">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" dataDxfId="5">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" dataDxfId="4">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="vlan-antall" dataDxfId="6" totalsRowDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="num_ports" dataDxfId="4" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" dataDxfId="2" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="vlan-antall" dataDxfId="3" totalsRowDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="num_ports" dataDxfId="2" totalsRowDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" dataDxfId="1" totalsRowDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" dataDxfId="0" totalsRowDxfId="18">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1390,7 +1434,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="46"/>
     <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{BBB41126-CDAD-40BD-92C3-0A8EEC64127E}" name="pri-1-10"/>
   </tableColumns>
@@ -1429,37 +1473,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="47" dataDxfId="46" totalsRowDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="45" dataDxfId="44" totalsRowDxfId="43">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="42">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" insertRow="1" headerRowDxfId="18" dataDxfId="17" totalsRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I25" headerRowDxfId="25" totalsRowDxfId="24">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="38">
+    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="15">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="37">
+    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="14">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="36">
+    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="13">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="12" totalsRowDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="11" totalsRowDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="10" totalsRowDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="9" totalsRowDxfId="35">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1492,7 +1536,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="34"/>
     <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{1CC9D42E-8B8D-4781-B4E6-7B024D0D4DB5}" name="pri-1-10"/>
   </tableColumns>
@@ -2150,19 +2194,141 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
+      <c r="A22" s="6">
+        <f>ROW()-21</f>
+        <v>1</v>
+      </c>
+      <c r="B22" s="6">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</f>
+        <v>10.11.0.2</v>
+      </c>
+      <c r="D22" s="6" t="str">
+        <f>$E$5</f>
+        <v>10.11.0.1</v>
+      </c>
+      <c r="E22" s="6" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F22" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="G22" s="11">
+        <v>4</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="11">
+        <f>$G22-3</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
+        <f>ROW()-21</f>
+        <v>2</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10</v>
+      </c>
+      <c r="C23" s="16" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
+        <v>10.11.0.3</v>
+      </c>
+      <c r="D23" s="16" t="str">
+        <f>$E$5</f>
+        <v>10.11.0.1</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="G23" s="11">
+        <v>4</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="17">
+        <f>$G23-3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6">
+        <f>ROW()-21</f>
+        <v>3</v>
+      </c>
+      <c r="B24" s="6">
+        <v>10</v>
+      </c>
+      <c r="C24" s="16" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
+        <v>10.11.0.4</v>
+      </c>
+      <c r="D24" s="16" t="str">
+        <f>$E$5</f>
+        <v>10.11.0.1</v>
+      </c>
+      <c r="E24" s="6" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="G24" s="11">
+        <v>4</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="17">
+        <f>$G24-3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6">
+        <f>ROW()-21</f>
+        <v>4</v>
+      </c>
+      <c r="B25" s="6">
+        <v>10</v>
+      </c>
+      <c r="C25" s="16" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A25)</f>
+        <v>10.11.0.5</v>
+      </c>
+      <c r="D25" s="16" t="str">
+        <f>$E$5</f>
+        <v>10.11.0.1</v>
+      </c>
+      <c r="E25" s="6" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F25" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="G25" s="11">
+        <v>4</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="17">
+        <f>$G25-3</f>
+        <v>1</v>
+      </c>
+    </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3141,7 +3307,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{E30D0828-D6F0-4F57-98C2-21AEB5B698E8}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F25" xr:uid="{D03F78DE-2965-48F5-B2E0-691EFE7B1D70}">
       <formula1>IF(F22="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(F22,"-"),"."))&lt;=$G22-3)</formula1>
     </dataValidation>
   </dataValidations>
@@ -3598,6 +3764,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
+        <f>ROW()-21</f>
         <v>1</v>
       </c>
       <c r="B22" s="6">
@@ -3615,22 +3782,88 @@
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F22" s="6">
-        <v>30.1</v>
+      <c r="F22" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="G22" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="11">
         <f>$G22-3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
+        <f>ROW()-21</f>
+        <v>2</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10</v>
+      </c>
+      <c r="C23" s="16" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
+        <v>10.12.0.3</v>
+      </c>
+      <c r="D23" s="16" t="str">
+        <f>$E$5</f>
+        <v>10.12.0.1</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="11">
+        <v>10</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="17">
+        <f>$G23-3</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6">
+        <f>ROW()-21</f>
+        <v>3</v>
+      </c>
+      <c r="B24" s="6">
+        <v>10</v>
+      </c>
+      <c r="C24" s="16" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
+        <v>10.12.0.4</v>
+      </c>
+      <c r="D24" s="16" t="str">
+        <f>$E$5</f>
+        <v>10.12.0.1</v>
+      </c>
+      <c r="E24" s="6" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>30.17</v>
+      </c>
+      <c r="G24" s="11">
+        <v>20</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="17">
+        <f>$G24-3</f>
+        <v>17</v>
+      </c>
+    </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4603,7 +4836,7 @@
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{95DCB370-0280-4896-A3B5-1510F9D5C323}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F24" xr:uid="{755C67B3-35A1-41CF-AFAD-859DFFCA6014}">
       <formula1>IF(F22="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(F22,"-"),"."))&lt;=$G22-3)</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575F4A5D-A441-4C0F-800A-E462E8EED511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E19B13-2439-4A0C-B471-D027FC47DA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -325,18 +325,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="111">
     <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -344,16 +341,25 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -394,11 +400,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -414,77 +419,9 @@
     </dxf>
     <dxf>
       <font>
-        <sz val="11"/>
+        <color theme="1"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -496,10 +433,28 @@
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -523,10 +478,11 @@
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -538,49 +494,87 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1383,39 +1377,39 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="33" dataDxfId="32" totalsRowDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="45" dataDxfId="44" totalsRowDxfId="43">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="42">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="39" totalsRowDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I24" headerRowDxfId="23" totalsRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I24" headerRowDxfId="37" totalsRowDxfId="36">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="35">
       <calculatedColumnFormula>ROW()-21</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" dataDxfId="33">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" dataDxfId="32">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" dataDxfId="31">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="vlan-antall" dataDxfId="3" totalsRowDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="num_ports" dataDxfId="2" totalsRowDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" dataDxfId="1" totalsRowDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" dataDxfId="0" totalsRowDxfId="18">
+    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="vlan-antall" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="num_ports" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1434,7 +1428,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="22"/>
     <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{BBB41126-CDAD-40BD-92C3-0A8EEC64127E}" name="pri-1-10"/>
   </tableColumns>
@@ -1473,37 +1467,37 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="45" dataDxfId="44" totalsRowDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="18">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I25" headerRowDxfId="25" totalsRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I25" headerRowDxfId="14" totalsRowDxfId="13">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="10">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="14">
+    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="9">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="13">
+    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="8">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="12" totalsRowDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="11" totalsRowDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="10" totalsRowDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="9" totalsRowDxfId="35">
+    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1536,7 +1530,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="46"/>
     <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{1CC9D42E-8B8D-4781-B4E6-7B024D0D4DB5}" name="pri-1-10"/>
   </tableColumns>
@@ -2235,11 +2229,11 @@
       <c r="B23" s="6">
         <v>10</v>
       </c>
-      <c r="C23" s="16" t="str">
+      <c r="C23" s="6" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
         <v>10.11.0.3</v>
       </c>
-      <c r="D23" s="16" t="str">
+      <c r="D23" s="6" t="str">
         <f>$E$5</f>
         <v>10.11.0.1</v>
       </c>
@@ -2256,7 +2250,7 @@
       <c r="H23" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="11">
         <f>$G23-3</f>
         <v>1</v>
       </c>
@@ -2269,11 +2263,11 @@
       <c r="B24" s="6">
         <v>10</v>
       </c>
-      <c r="C24" s="16" t="str">
+      <c r="C24" s="6" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
         <v>10.11.0.4</v>
       </c>
-      <c r="D24" s="16" t="str">
+      <c r="D24" s="6" t="str">
         <f>$E$5</f>
         <v>10.11.0.1</v>
       </c>
@@ -2290,7 +2284,7 @@
       <c r="H24" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="11">
         <f>$G24-3</f>
         <v>1</v>
       </c>
@@ -2303,11 +2297,11 @@
       <c r="B25" s="6">
         <v>10</v>
       </c>
-      <c r="C25" s="16" t="str">
+      <c r="C25" s="6" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A25)</f>
         <v>10.11.0.5</v>
       </c>
-      <c r="D25" s="16" t="str">
+      <c r="D25" s="6" t="str">
         <f>$E$5</f>
         <v>10.11.0.1</v>
       </c>
@@ -2324,7 +2318,7 @@
       <c r="H25" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="11">
         <f>$G25-3</f>
         <v>1</v>
       </c>
@@ -3804,11 +3798,11 @@
       <c r="B23" s="6">
         <v>10</v>
       </c>
-      <c r="C23" s="16" t="str">
+      <c r="C23" s="6" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
         <v>10.12.0.3</v>
       </c>
-      <c r="D23" s="16" t="str">
+      <c r="D23" s="6" t="str">
         <f>$E$5</f>
         <v>10.12.0.1</v>
       </c>
@@ -3825,7 +3819,7 @@
       <c r="H23" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="11">
         <f>$G23-3</f>
         <v>7</v>
       </c>
@@ -3838,11 +3832,11 @@
       <c r="B24" s="6">
         <v>10</v>
       </c>
-      <c r="C24" s="16" t="str">
+      <c r="C24" s="6" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
         <v>10.12.0.4</v>
       </c>
-      <c r="D24" s="16" t="str">
+      <c r="D24" s="6" t="str">
         <f>$E$5</f>
         <v>10.12.0.1</v>
       </c>
@@ -3851,7 +3845,7 @@
         <v>255.255.0.0</v>
       </c>
       <c r="F24" s="6">
-        <v>30.17</v>
+        <v>30.1</v>
       </c>
       <c r="G24" s="11">
         <v>20</v>
@@ -3859,7 +3853,7 @@
       <c r="H24" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="11">
         <f>$G24-3</f>
         <v>17</v>
       </c>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E19B13-2439-4A0C-B471-D027FC47DA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D2BFBB-20F5-4993-BD44-26EF119EB636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="49">
   <si>
     <t>site</t>
   </si>
@@ -181,12 +181,6 @@
   </si>
   <si>
     <t>pri-afxx</t>
-  </si>
-  <si>
-    <t>30.2-20.5</t>
-  </si>
-  <si>
-    <t>20.1-10.1</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1385,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I24" headerRowDxfId="37" totalsRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I22" headerRowDxfId="37" totalsRowDxfId="36">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="35">
       <calculatedColumnFormula>ROW()-21</calculatedColumnFormula>
@@ -1481,7 +1475,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I25" headerRowDxfId="14" totalsRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" insertRow="1" headerRowDxfId="14" totalsRowDxfId="13">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="11"/>
@@ -2188,141 +2182,19 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
-        <f>ROW()-21</f>
-        <v>1</v>
-      </c>
-      <c r="B22" s="6">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</f>
-        <v>10.11.0.2</v>
-      </c>
-      <c r="D22" s="6" t="str">
-        <f>$E$5</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="E22" s="6" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="G22" s="11">
-        <v>4</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="11">
-        <f>$G22-3</f>
-        <v>1</v>
-      </c>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
-        <f>ROW()-21</f>
-        <v>2</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
-        <v>10.11.0.3</v>
-      </c>
-      <c r="D23" s="6" t="str">
-        <f>$E$5</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="E23" s="6" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="G23" s="11">
-        <v>4</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="11">
-        <f>$G23-3</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
-        <f>ROW()-21</f>
-        <v>3</v>
-      </c>
-      <c r="B24" s="6">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
-        <v>10.11.0.4</v>
-      </c>
-      <c r="D24" s="6" t="str">
-        <f>$E$5</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="E24" s="6" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="G24" s="11">
-        <v>4</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="11">
-        <f>$G24-3</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
-        <f>ROW()-21</f>
-        <v>4</v>
-      </c>
-      <c r="B25" s="6">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A25)</f>
-        <v>10.11.0.5</v>
-      </c>
-      <c r="D25" s="6" t="str">
-        <f>$E$5</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="E25" s="6" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="G25" s="11">
-        <v>4</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="11">
-        <f>$G25-3</f>
-        <v>1</v>
-      </c>
-    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3301,7 +3173,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F25" xr:uid="{D03F78DE-2965-48F5-B2E0-691EFE7B1D70}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{D03F78DE-2965-48F5-B2E0-691EFE7B1D70}">
       <formula1>IF(F22="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(F22,"-"),"."))&lt;=$G22-3)</formula1>
     </dataValidation>
   </dataValidations>
@@ -3776,88 +3648,22 @@
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>50</v>
+      <c r="F22" s="6">
+        <v>20.100000000000001</v>
       </c>
       <c r="G22" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="11">
         <f>$G22-3</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
-        <f>ROW()-21</f>
-        <v>2</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
-        <v>10.12.0.3</v>
-      </c>
-      <c r="D23" s="6" t="str">
-        <f>$E$5</f>
-        <v>10.12.0.1</v>
-      </c>
-      <c r="E23" s="6" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="11">
-        <v>10</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="11">
-        <f>$G23-3</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
-        <f>ROW()-21</f>
-        <v>3</v>
-      </c>
-      <c r="B24" s="6">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
-        <v>10.12.0.4</v>
-      </c>
-      <c r="D24" s="6" t="str">
-        <f>$E$5</f>
-        <v>10.12.0.1</v>
-      </c>
-      <c r="E24" s="6" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="G24" s="11">
-        <v>20</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="11">
-        <f>$G24-3</f>
-        <v>17</v>
-      </c>
-    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4830,7 +4636,7 @@
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F24" xr:uid="{755C67B3-35A1-41CF-AFAD-859DFFCA6014}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{755C67B3-35A1-41CF-AFAD-859DFFCA6014}">
       <formula1>IF(F22="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(F22,"-"),"."))&lt;=$G22-3)</formula1>
     </dataValidation>
   </dataValidations>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D2BFBB-20F5-4993-BD44-26EF119EB636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7511A592-264A-48D3-A91D-D72E2E5CAFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="50">
   <si>
     <t>site</t>
   </si>
@@ -57,9 +57,6 @@
     <t>admin</t>
   </si>
   <si>
-    <t>cisco</t>
-  </si>
-  <si>
     <t>0 - 4</t>
   </si>
   <si>
@@ -181,6 +178,12 @@
   </si>
   <si>
     <t>pri-afxx</t>
+  </si>
+  <si>
+    <t>secret</t>
+  </si>
+  <si>
+    <t>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</t>
   </si>
 </sst>
 </file>
@@ -323,7 +326,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="111">
+  <dxfs count="117">
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -398,6 +401,159 @@
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -469,108 +625,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -581,12 +635,12 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1231,100 +1285,100 @@
   </dxfs>
   <tableStyles count="16">
     <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="110"/>
-      <tableStyleElement type="headerRow" dxfId="109"/>
-      <tableStyleElement type="firstRowStripe" dxfId="108"/>
-      <tableStyleElement type="secondRowStripe" dxfId="107"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="116"/>
+      <tableStyleElement type="headerRow" dxfId="115"/>
+      <tableStyleElement type="firstRowStripe" dxfId="114"/>
+      <tableStyleElement type="secondRowStripe" dxfId="113"/>
     </tableStyle>
     <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="106"/>
-      <tableStyleElement type="headerRow" dxfId="105"/>
-      <tableStyleElement type="firstRowStripe" dxfId="104"/>
-      <tableStyleElement type="secondRowStripe" dxfId="103"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="112"/>
+      <tableStyleElement type="headerRow" dxfId="111"/>
+      <tableStyleElement type="firstRowStripe" dxfId="110"/>
+      <tableStyleElement type="secondRowStripe" dxfId="109"/>
     </tableStyle>
     <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="102"/>
-      <tableStyleElement type="headerRow" dxfId="101"/>
-      <tableStyleElement type="firstRowStripe" dxfId="100"/>
-      <tableStyleElement type="secondRowStripe" dxfId="99"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="108"/>
+      <tableStyleElement type="headerRow" dxfId="107"/>
+      <tableStyleElement type="firstRowStripe" dxfId="106"/>
+      <tableStyleElement type="secondRowStripe" dxfId="105"/>
     </tableStyle>
     <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="98"/>
-      <tableStyleElement type="headerRow" dxfId="97"/>
-      <tableStyleElement type="firstRowStripe" dxfId="96"/>
-      <tableStyleElement type="secondRowStripe" dxfId="95"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="104"/>
+      <tableStyleElement type="headerRow" dxfId="103"/>
+      <tableStyleElement type="firstRowStripe" dxfId="102"/>
+      <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
     <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="94"/>
-      <tableStyleElement type="headerRow" dxfId="93"/>
-      <tableStyleElement type="firstRowStripe" dxfId="92"/>
-      <tableStyleElement type="secondRowStripe" dxfId="91"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
+      <tableStyleElement type="headerRow" dxfId="99"/>
+      <tableStyleElement type="firstRowStripe" dxfId="98"/>
+      <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
-      <tableStyleElement type="headerRow" dxfId="89"/>
-      <tableStyleElement type="firstRowStripe" dxfId="88"/>
-      <tableStyleElement type="secondRowStripe" dxfId="87"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="96"/>
+      <tableStyleElement type="headerRow" dxfId="95"/>
+      <tableStyleElement type="firstRowStripe" dxfId="94"/>
+      <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
     <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="86"/>
-      <tableStyleElement type="headerRow" dxfId="85"/>
-      <tableStyleElement type="firstRowStripe" dxfId="84"/>
-      <tableStyleElement type="secondRowStripe" dxfId="83"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="92"/>
+      <tableStyleElement type="headerRow" dxfId="91"/>
+      <tableStyleElement type="firstRowStripe" dxfId="90"/>
+      <tableStyleElement type="secondRowStripe" dxfId="89"/>
     </tableStyle>
     <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="82"/>
-      <tableStyleElement type="headerRow" dxfId="81"/>
-      <tableStyleElement type="firstRowStripe" dxfId="80"/>
-      <tableStyleElement type="secondRowStripe" dxfId="79"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="88"/>
+      <tableStyleElement type="headerRow" dxfId="87"/>
+      <tableStyleElement type="firstRowStripe" dxfId="86"/>
+      <tableStyleElement type="secondRowStripe" dxfId="85"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
-      <tableStyleElement type="headerRow" dxfId="77"/>
-      <tableStyleElement type="firstRowStripe" dxfId="76"/>
-      <tableStyleElement type="secondRowStripe" dxfId="75"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
+      <tableStyleElement type="headerRow" dxfId="83"/>
+      <tableStyleElement type="firstRowStripe" dxfId="82"/>
+      <tableStyleElement type="secondRowStripe" dxfId="81"/>
     </tableStyle>
     <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="74"/>
-      <tableStyleElement type="headerRow" dxfId="73"/>
-      <tableStyleElement type="firstRowStripe" dxfId="72"/>
-      <tableStyleElement type="secondRowStripe" dxfId="71"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="80"/>
+      <tableStyleElement type="headerRow" dxfId="79"/>
+      <tableStyleElement type="firstRowStripe" dxfId="78"/>
+      <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
     <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="70"/>
-      <tableStyleElement type="headerRow" dxfId="69"/>
-      <tableStyleElement type="firstRowStripe" dxfId="68"/>
-      <tableStyleElement type="secondRowStripe" dxfId="67"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="76"/>
+      <tableStyleElement type="headerRow" dxfId="75"/>
+      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="66"/>
-      <tableStyleElement type="headerRow" dxfId="65"/>
-      <tableStyleElement type="firstRowStripe" dxfId="64"/>
-      <tableStyleElement type="secondRowStripe" dxfId="63"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="72"/>
+      <tableStyleElement type="headerRow" dxfId="71"/>
+      <tableStyleElement type="firstRowStripe" dxfId="70"/>
+      <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
     <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="62"/>
-      <tableStyleElement type="headerRow" dxfId="61"/>
-      <tableStyleElement type="firstRowStripe" dxfId="60"/>
-      <tableStyleElement type="secondRowStripe" dxfId="59"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="68"/>
+      <tableStyleElement type="headerRow" dxfId="67"/>
+      <tableStyleElement type="firstRowStripe" dxfId="66"/>
+      <tableStyleElement type="secondRowStripe" dxfId="65"/>
     </tableStyle>
     <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="58"/>
-      <tableStyleElement type="headerRow" dxfId="57"/>
-      <tableStyleElement type="firstRowStripe" dxfId="56"/>
-      <tableStyleElement type="secondRowStripe" dxfId="55"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="64"/>
+      <tableStyleElement type="headerRow" dxfId="63"/>
+      <tableStyleElement type="firstRowStripe" dxfId="62"/>
+      <tableStyleElement type="secondRowStripe" dxfId="61"/>
     </tableStyle>
     <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="54"/>
-      <tableStyleElement type="headerRow" dxfId="53"/>
-      <tableStyleElement type="firstRowStripe" dxfId="52"/>
-      <tableStyleElement type="secondRowStripe" dxfId="51"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="60"/>
+      <tableStyleElement type="headerRow" dxfId="59"/>
+      <tableStyleElement type="firstRowStripe" dxfId="58"/>
+      <tableStyleElement type="secondRowStripe" dxfId="57"/>
     </tableStyle>
     <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="50"/>
-      <tableStyleElement type="headerRow" dxfId="49"/>
-      <tableStyleElement type="firstRowStripe" dxfId="48"/>
-      <tableStyleElement type="secondRowStripe" dxfId="47"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="56"/>
+      <tableStyleElement type="headerRow" dxfId="55"/>
+      <tableStyleElement type="firstRowStripe" dxfId="54"/>
+      <tableStyleElement type="secondRowStripe" dxfId="53"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1339,14 +1393,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:F2">
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:G2">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="router-id"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
+    <tableColumn id="7" xr3:uid="{754ADF79-920D-4601-911B-DB20F4E9EEB9}" name="secret" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="Site 1 (HUB)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1371,39 +1426,40 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:D19" headerRowDxfId="45" dataDxfId="44" totalsRowDxfId="43">
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A18:E19" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="21">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{E8DA5B0D-4B09-4D1E-BDAB-BAC231407C4D}" name="secret" dataDxfId="16" totalsRowDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I22" headerRowDxfId="37" totalsRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A21:I22" headerRowDxfId="14" totalsRowDxfId="13">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="12">
       <calculatedColumnFormula>ROW()-21</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" dataDxfId="33">
+    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" dataDxfId="10">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" dataDxfId="32">
+    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" dataDxfId="9">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" dataDxfId="31">
+    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" dataDxfId="8">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="vlan-antall" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="num_ports" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" dataDxfId="24" totalsRowDxfId="23">
+    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="vlan-antall" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="num_ports" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1422,7 +1478,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="51"/>
     <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{BBB41126-CDAD-40BD-92C3-0A8EEC64127E}" name="pri-1-10"/>
   </tableColumns>
@@ -1461,37 +1517,38 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:D19" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A18:E19" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="47">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{E15E69AB-85DA-4C56-B495-1EB315268322}" name="secret" dataDxfId="43" totalsRowDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" insertRow="1" headerRowDxfId="14" totalsRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A21:I22" insertRow="1" headerRowDxfId="41" totalsRowDxfId="40">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="37">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="36">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="35">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="1" totalsRowDxfId="0">
+    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="28" totalsRowDxfId="27">
       <calculatedColumnFormula>$G22-3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1500,14 +1557,15 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell1" displayName="Tabell1" ref="A1:F2">
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell1" displayName="Tabell1" ref="A1:G2">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="intf_prefix"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="router-id"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="vty_lines"/>
+    <tableColumn id="7" xr3:uid="{AB00FC62-D408-4EC3-87DF-1FBB1D6A67CC}" name="secret" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="Site 2-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1524,7 +1582,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="25"/>
     <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{1CC9D42E-8B8D-4781-B4E6-7B024D0D4DB5}" name="pri-1-10"/>
   </tableColumns>
@@ -1775,13 +1833,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
@@ -1791,10 +1852,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
+      <c r="G2" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1809,42 +1873,42 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="7">
         <v>10</v>
@@ -1861,7 +1925,7 @@
         <v>10.11.0.1</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
@@ -1883,7 +1947,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="7">
         <v>20</v>
@@ -1900,7 +1964,7 @@
         <v>10.21.0.1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1922,7 +1986,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7">
         <v>30</v>
@@ -1939,7 +2003,7 @@
         <v>10.31.0.1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1965,24 +2029,24 @@
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="6">
         <v>10</v>
@@ -1994,10 +2058,10 @@
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="6">
         <v>20</v>
@@ -2009,10 +2073,10 @@
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="6">
         <v>30</v>
@@ -2025,49 +2089,49 @@
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
@@ -2075,7 +2139,7 @@
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15" s="2">
         <v>10</v>
@@ -2085,17 +2149,17 @@
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.31</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
@@ -2103,7 +2167,7 @@
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
@@ -2135,6 +2199,9 @@
       <c r="D18" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="E18" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="11">
@@ -2145,40 +2212,43 @@
         <v>6</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>8</v>
+      <c r="E19" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>1</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3226,13 +3296,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
@@ -3242,10 +3315,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
+      <c r="G2" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3260,42 +3336,42 @@
     </row>
     <row r="4" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="I4" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="7">
         <v>10</v>
@@ -3312,7 +3388,7 @@
         <v>10.12.0.1</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="6" t="str">
         <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
@@ -3334,7 +3410,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="7">
         <v>20</v>
@@ -3351,7 +3427,7 @@
         <v>10.22.0.1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3373,7 +3449,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7">
         <v>30</v>
@@ -3390,7 +3466,7 @@
         <v>10.32.0.1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="6" t="str">
         <f t="shared" si="1"/>
@@ -3416,24 +3492,24 @@
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="6">
         <v>10</v>
@@ -3445,10 +3521,10 @@
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="6">
         <v>20</v>
@@ -3460,10 +3536,10 @@
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="6">
         <v>30</v>
@@ -3476,49 +3552,49 @@
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="I14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="J14" s="13" t="s">
         <v>33</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+A2)</f>
         <v>172.16.0.12</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H15</f>
@@ -3526,7 +3602,7 @@
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15" s="2">
         <v>10</v>
@@ -3539,17 +3615,17 @@
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+A2)</f>
         <v>172.16.0.32</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="6" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;H16</f>
@@ -3557,7 +3633,7 @@
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
@@ -3582,6 +3658,9 @@
       <c r="D18" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="E18" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="11">
@@ -3592,40 +3671,43 @@
         <v>6</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>8</v>
+      <c r="E19" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>1</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3655,7 +3737,7 @@
         <v>4</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I22" s="11">
         <f>$G22-3</f>
